--- a/results/2026-04-07-SAT-precedence-graph/results_maxsat_scl_infsteps180_prec_graph_120s.xlsx
+++ b/results/2026-04-07-SAT-precedence-graph/results_maxsat_scl_infsteps180_prec_graph_120s.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17715"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="34515"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <connection id="1" name="results_maxsat_scl_infsteps180_prec_graph_120s" type="6" refreshedVersion="5" background="1" saveData="1">
-    <textPr codePage="437" sourceFile="D:\github\maxsattrainscheduling\results\2026-04-07-SAT-precedence-graph\raw_data\csv\results_maxsat_scl_infsteps180_prec_graph_120s.csv" comma="1">
+    <textPr codePage="437" sourceFile="D:\github\maxsattrainscheduling\results_maxsat_scl_infsteps180_prec_graph_120s.csv" comma="1">
       <textFields count="26">
         <textField/>
         <textField/>
@@ -249,16 +249,16 @@
     <t>trackA8</t>
   </si>
   <si>
+    <t>trackA9</t>
+  </si>
+  <si>
+    <t>trackA10</t>
+  </si>
+  <si>
+    <t>trackA11</t>
+  </si>
+  <si>
     <t>timeout</t>
-  </si>
-  <si>
-    <t>trackA9</t>
-  </si>
-  <si>
-    <t>trackA10</t>
-  </si>
-  <si>
-    <t>trackA11</t>
   </si>
   <si>
     <t>trackA12</t>
@@ -846,10 +846,10 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>2.8286856999999999E-2</v>
+        <v>0.58261106100000004</v>
       </c>
       <c r="B2">
-        <v>1.4207562349155201</v>
+        <v>1.5478680611423901</v>
       </c>
       <c r="C2">
         <v>20.931034088134702</v>
@@ -861,7 +861,7 @@
         <v>33</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="G2" t="s">
         <v>26</v>
@@ -870,78 +870,78 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="J2">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="K2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L2" t="s">
         <v>27</v>
       </c>
       <c r="M2">
-        <v>459</v>
+        <v>582</v>
       </c>
       <c r="N2">
-        <v>1766</v>
+        <v>1924</v>
       </c>
       <c r="O2">
-        <v>459</v>
+        <v>582</v>
       </c>
       <c r="P2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q2">
         <v>1</v>
       </c>
       <c r="R2">
-        <v>30.096081000000002</v>
+        <v>586.55093399999998</v>
       </c>
       <c r="S2" t="s">
         <v>28</v>
       </c>
       <c r="T2">
-        <v>1.671699E-3</v>
+        <v>3.0466159999999998E-3</v>
       </c>
       <c r="U2" t="s">
         <v>29</v>
       </c>
       <c r="V2">
-        <v>2.9958002000000001E-2</v>
+        <v>0.585657184</v>
       </c>
       <c r="W2">
         <v>29</v>
       </c>
       <c r="X2">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="Y2">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Z2">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="AB2" s="3">
         <f>AVERAGE(R2:R25)</f>
-        <v>26.390763208333329</v>
+        <v>45.549405874999998</v>
       </c>
       <c r="AC2" s="3">
         <f>AVERAGE(R26:R49)</f>
-        <v>15319.752562291671</v>
+        <v>10110.923160374999</v>
       </c>
       <c r="AD2" s="3">
         <f>AVERAGE(R50:R73)</f>
-        <v>15894.958267041669</v>
+        <v>9970.8928950833306</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>1.5817167E-2</v>
+        <v>3.1185185000000001E-2</v>
       </c>
       <c r="B3">
-        <v>1.6051282051282001</v>
+        <v>1.8594871794871699</v>
       </c>
       <c r="C3">
         <v>19</v>
@@ -953,7 +953,7 @@
         <v>33</v>
       </c>
       <c r="F3">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="G3" t="s">
         <v>26</v>
@@ -962,66 +962,66 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J3">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="K3">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L3" t="s">
         <v>30</v>
       </c>
       <c r="M3">
-        <v>460</v>
+        <v>691</v>
       </c>
       <c r="N3">
-        <v>1565</v>
+        <v>1813</v>
       </c>
       <c r="O3">
-        <v>460</v>
+        <v>691</v>
       </c>
       <c r="P3">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="Q3">
         <v>1</v>
       </c>
       <c r="R3">
-        <v>20.819813</v>
+        <v>34.56653</v>
       </c>
       <c r="S3" t="s">
         <v>28</v>
       </c>
       <c r="T3">
-        <v>4.8754719999999996E-3</v>
+        <v>3.2462770000000001E-3</v>
       </c>
       <c r="U3" t="s">
         <v>29</v>
       </c>
       <c r="V3">
-        <v>2.0692135E-2</v>
+        <v>3.4430892999999997E-2</v>
       </c>
       <c r="W3">
         <v>25</v>
       </c>
       <c r="X3">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="Y3">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Z3">
-        <v>37</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>1.3896277E-2</v>
+        <v>1.2234138E-2</v>
       </c>
       <c r="B4">
-        <v>1.47814207650273</v>
+        <v>1.0327868852458999</v>
       </c>
       <c r="C4">
         <v>22.375</v>
@@ -1042,55 +1042,55 @@
         <v>2</v>
       </c>
       <c r="I4">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="J4">
         <v>14</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L4" t="s">
         <v>31</v>
       </c>
       <c r="M4">
-        <v>310</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>1082</v>
+        <v>756</v>
       </c>
       <c r="O4">
-        <v>310</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Q4">
         <v>1</v>
       </c>
       <c r="R4">
-        <v>15.070758</v>
+        <v>12.28528</v>
       </c>
       <c r="S4" t="s">
         <v>28</v>
       </c>
-      <c r="T4">
-        <v>1.12718E-3</v>
+      <c r="T4" s="1">
+        <v>8.3659999999999992E-6</v>
       </c>
       <c r="U4" t="s">
         <v>29</v>
       </c>
       <c r="V4">
-        <v>1.5022931999999999E-2</v>
+        <v>1.2241874999999999E-2</v>
       </c>
       <c r="W4">
         <v>16</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="Z4">
         <v>14</v>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>1.3564174E-2</v>
+        <v>1.4702784999999999E-2</v>
       </c>
       <c r="B5">
-        <v>1.63224637681159</v>
+        <v>1.5688405797101399</v>
       </c>
       <c r="C5">
         <v>19.214284896850501</v>
@@ -1113,7 +1113,7 @@
         <v>33</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5" t="s">
         <v>26</v>
@@ -1122,46 +1122,46 @@
         <v>3</v>
       </c>
       <c r="I5">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="J5">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L5" t="s">
         <v>32</v>
       </c>
       <c r="M5">
-        <v>309</v>
+        <v>250</v>
       </c>
       <c r="N5">
-        <v>901</v>
+        <v>866</v>
       </c>
       <c r="O5">
-        <v>309</v>
+        <v>250</v>
       </c>
       <c r="P5">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="Q5">
         <v>1</v>
       </c>
       <c r="R5">
-        <v>15.111993999999999</v>
+        <v>15.290677000000001</v>
       </c>
       <c r="S5" t="s">
         <v>28</v>
       </c>
       <c r="T5">
-        <v>1.49909E-3</v>
+        <v>5.4340200000000001E-4</v>
       </c>
       <c r="U5" t="s">
         <v>29</v>
       </c>
       <c r="V5">
-        <v>1.5062432000000001E-2</v>
+        <v>1.524557E-2</v>
       </c>
       <c r="W5">
         <v>14</v>
@@ -1170,18 +1170,18 @@
         <v>10</v>
       </c>
       <c r="Y5">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="Z5">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>1.4105137E-2</v>
+        <v>1.5279698E-2</v>
       </c>
       <c r="B6">
-        <v>1.5421940928269999</v>
+        <v>1.75949367088607</v>
       </c>
       <c r="C6">
         <v>19.25</v>
@@ -1193,7 +1193,7 @@
         <v>33</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
         <v>26</v>
@@ -1202,66 +1202,66 @@
         <v>4</v>
       </c>
       <c r="I6">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="J6">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L6" t="s">
         <v>33</v>
       </c>
       <c r="M6">
-        <v>220</v>
+        <v>304</v>
       </c>
       <c r="N6">
-        <v>731</v>
+        <v>834</v>
       </c>
       <c r="O6">
-        <v>220</v>
+        <v>304</v>
       </c>
       <c r="P6">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Q6">
         <v>1</v>
       </c>
       <c r="R6">
-        <v>15.496183</v>
+        <v>16.159929000000002</v>
       </c>
       <c r="S6" t="s">
         <v>28</v>
       </c>
       <c r="T6">
-        <v>1.327944E-3</v>
+        <v>8.3254900000000003E-4</v>
       </c>
       <c r="U6" t="s">
         <v>29</v>
       </c>
       <c r="V6">
-        <v>1.5432558000000001E-2</v>
+        <v>1.6111716000000002E-2</v>
       </c>
       <c r="W6">
         <v>12</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Y6">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="Z6">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>1.370093E-2</v>
+        <v>1.1654457E-2</v>
       </c>
       <c r="B7">
-        <v>1.73856209150326</v>
+        <v>1.0392156862744999</v>
       </c>
       <c r="C7">
         <v>18.625</v>
@@ -1273,7 +1273,7 @@
         <v>33</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G7" t="s">
         <v>26</v>
@@ -1282,66 +1282,66 @@
         <v>5</v>
       </c>
       <c r="I7">
-        <v>102</v>
+        <v>4</v>
       </c>
       <c r="J7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L7" t="s">
         <v>34</v>
       </c>
       <c r="M7">
-        <v>206</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>532</v>
+        <v>318</v>
       </c>
       <c r="O7">
-        <v>206</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Q7">
         <v>1</v>
       </c>
       <c r="R7">
-        <v>15.024462</v>
+        <v>11.681419999999999</v>
       </c>
       <c r="S7" t="s">
         <v>28</v>
       </c>
-      <c r="T7">
-        <v>1.293151E-3</v>
+      <c r="T7" s="1">
+        <v>7.9039999999999992E-6</v>
       </c>
       <c r="U7" t="s">
         <v>29</v>
       </c>
       <c r="V7">
-        <v>1.4993585E-2</v>
+        <v>1.1661796E-2</v>
       </c>
       <c r="W7">
         <v>8</v>
       </c>
       <c r="X7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y7">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="Z7">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>1.26625349999999E-2</v>
+        <v>1.1984702999999999E-2</v>
       </c>
       <c r="B8">
-        <v>1.8047619047618999</v>
+        <v>1.09523809523809</v>
       </c>
       <c r="C8">
         <v>12.625</v>
@@ -1362,55 +1362,55 @@
         <v>6</v>
       </c>
       <c r="I8">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="J8">
         <v>15</v>
       </c>
       <c r="K8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L8" t="s">
         <v>35</v>
       </c>
       <c r="M8">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="N8">
-        <v>379</v>
+        <v>230</v>
       </c>
       <c r="O8">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Q8">
         <v>1</v>
       </c>
       <c r="R8">
-        <v>13.433012</v>
+        <v>12.009371</v>
       </c>
       <c r="S8" t="s">
         <v>28</v>
       </c>
-      <c r="T8">
-        <v>7.47031E-4</v>
+      <c r="T8" s="1">
+        <v>8.9849999999999995E-6</v>
       </c>
       <c r="U8" t="s">
         <v>29</v>
       </c>
       <c r="V8">
-        <v>1.3409067E-2</v>
+        <v>1.1992857000000001E-2</v>
       </c>
       <c r="W8">
         <v>8</v>
       </c>
       <c r="X8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Z8">
         <v>15</v>
@@ -1418,10 +1418,10 @@
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>2.9466458000000001E-2</v>
+        <v>3.4792869999999997E-2</v>
       </c>
       <c r="B9">
-        <v>2.63949275362318</v>
+        <v>2.92481884057971</v>
       </c>
       <c r="C9">
         <v>19.214284896850501</v>
@@ -1433,7 +1433,7 @@
         <v>33</v>
       </c>
       <c r="F9">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="G9" t="s">
         <v>26</v>
@@ -1442,66 +1442,66 @@
         <v>7</v>
       </c>
       <c r="I9">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="J9">
-        <v>142</v>
+        <v>255</v>
       </c>
       <c r="K9">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L9" t="s">
         <v>36</v>
       </c>
       <c r="M9">
-        <v>1358</v>
+        <v>1571</v>
       </c>
       <c r="N9">
-        <v>2914</v>
+        <v>3229</v>
       </c>
       <c r="O9">
-        <v>1358</v>
+        <v>1571</v>
       </c>
       <c r="P9">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="Q9">
         <v>1</v>
       </c>
       <c r="R9">
-        <v>139.10500500000001</v>
+        <v>49.070977999999997</v>
       </c>
       <c r="S9" t="s">
         <v>28</v>
       </c>
       <c r="T9">
-        <v>0.109442443</v>
+        <v>1.4031004999999999E-2</v>
       </c>
       <c r="U9" t="s">
         <v>29</v>
       </c>
       <c r="V9">
-        <v>0.138908316</v>
+        <v>4.8823225999999997E-2</v>
       </c>
       <c r="W9">
         <v>28</v>
       </c>
       <c r="X9">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Z9">
-        <v>142</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>1.6351870000000001E-2</v>
+        <v>2.7455358999999999E-2</v>
       </c>
       <c r="B10">
-        <v>2.24817518248175</v>
+        <v>1.96836982968369</v>
       </c>
       <c r="C10">
         <v>20.049999237060501</v>
@@ -1513,7 +1513,7 @@
         <v>33</v>
       </c>
       <c r="F10">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="G10" t="s">
         <v>26</v>
@@ -1522,66 +1522,66 @@
         <v>8</v>
       </c>
       <c r="I10">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J10">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="K10">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L10" t="s">
         <v>37</v>
       </c>
       <c r="M10">
-        <v>845</v>
+        <v>631</v>
       </c>
       <c r="N10">
-        <v>1848</v>
+        <v>1618</v>
       </c>
       <c r="O10">
-        <v>845</v>
+        <v>631</v>
       </c>
       <c r="P10">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="Q10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R10">
-        <v>27.812781000000001</v>
+        <v>28.979727</v>
       </c>
       <c r="S10" t="s">
         <v>28</v>
       </c>
       <c r="T10">
-        <v>1.1317944E-2</v>
+        <v>1.398739E-3</v>
       </c>
       <c r="U10" t="s">
         <v>29</v>
       </c>
       <c r="V10">
-        <v>2.7669103E-2</v>
+        <v>2.8853588999999999E-2</v>
       </c>
       <c r="W10">
         <v>20</v>
       </c>
       <c r="X10">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="Y10">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="Z10">
-        <v>41</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>1.6068931000000002E-2</v>
+        <v>1.9076843999999999E-2</v>
       </c>
       <c r="B11">
-        <v>2.4551181102362198</v>
+        <v>2.9779527559055099</v>
       </c>
       <c r="C11">
         <v>18.176469802856399</v>
@@ -1593,7 +1593,7 @@
         <v>33</v>
       </c>
       <c r="F11">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="G11" t="s">
         <v>26</v>
@@ -1602,66 +1602,66 @@
         <v>9</v>
       </c>
       <c r="I11">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="J11">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="K11">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="L11" t="s">
         <v>38</v>
       </c>
       <c r="M11">
-        <v>791</v>
+        <v>1040</v>
       </c>
       <c r="N11">
-        <v>1559</v>
+        <v>1891</v>
       </c>
       <c r="O11">
-        <v>791</v>
+        <v>1040</v>
       </c>
       <c r="P11">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="Q11">
         <v>1</v>
       </c>
       <c r="R11">
-        <v>21.414794000000001</v>
+        <v>24.630042</v>
       </c>
       <c r="S11" t="s">
         <v>28</v>
       </c>
       <c r="T11">
-        <v>5.2407640000000002E-3</v>
+        <v>5.422601E-3</v>
       </c>
       <c r="U11" t="s">
         <v>29</v>
       </c>
       <c r="V11">
-        <v>2.1309116999999999E-2</v>
+        <v>2.4498819000000002E-2</v>
       </c>
       <c r="W11">
         <v>17</v>
       </c>
       <c r="X11">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="Y11">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="Z11">
-        <v>33</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>2.7753778E-2</v>
+        <v>4.3806507999999897E-2</v>
       </c>
       <c r="B12">
-        <v>1.8721311475409801</v>
+        <v>2.1319672131147498</v>
       </c>
       <c r="C12">
         <v>19.8333339691162</v>
@@ -1673,7 +1673,7 @@
         <v>33</v>
       </c>
       <c r="F12">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G12" t="s">
         <v>26</v>
@@ -1682,66 +1682,66 @@
         <v>10</v>
       </c>
       <c r="I12">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="J12">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L12" t="s">
         <v>39</v>
       </c>
       <c r="M12">
-        <v>882</v>
+        <v>1168</v>
       </c>
       <c r="N12">
-        <v>2284</v>
+        <v>2601</v>
       </c>
       <c r="O12">
-        <v>882</v>
+        <v>1168</v>
       </c>
       <c r="P12">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="Q12">
         <v>1</v>
       </c>
       <c r="R12">
-        <v>53.690503</v>
+        <v>63.874343000000003</v>
       </c>
       <c r="S12" t="s">
         <v>28</v>
       </c>
       <c r="T12">
-        <v>2.5782866000000002E-2</v>
+        <v>1.9856728000000001E-2</v>
       </c>
       <c r="U12" t="s">
         <v>29</v>
       </c>
       <c r="V12">
-        <v>5.3536040999999999E-2</v>
+        <v>6.3662710999999997E-2</v>
       </c>
       <c r="W12">
         <v>30</v>
       </c>
       <c r="X12">
+        <v>56</v>
+      </c>
+      <c r="Y12">
         <v>41</v>
       </c>
-      <c r="Y12">
-        <v>25</v>
-      </c>
       <c r="Z12">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>2.9785580999999901E-2</v>
+        <v>4.1956563999999898E-2</v>
       </c>
       <c r="B13">
-        <v>1.97588424437299</v>
+        <v>2.0546623794212202</v>
       </c>
       <c r="C13">
         <v>21.714284896850501</v>
@@ -1762,66 +1762,66 @@
         <v>11</v>
       </c>
       <c r="I13">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="J13">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K13">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L13" t="s">
         <v>40</v>
       </c>
       <c r="M13">
-        <v>977</v>
+        <v>1073</v>
       </c>
       <c r="N13">
-        <v>2458</v>
+        <v>2556</v>
       </c>
       <c r="O13">
-        <v>977</v>
+        <v>1073</v>
       </c>
       <c r="P13">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="Q13">
         <v>1</v>
       </c>
       <c r="R13">
-        <v>82.477428000000003</v>
+        <v>56.988222</v>
       </c>
       <c r="S13" t="s">
         <v>28</v>
       </c>
       <c r="T13">
-        <v>5.2524946000000003E-2</v>
+        <v>1.485936E-2</v>
       </c>
       <c r="U13" t="s">
         <v>29</v>
       </c>
       <c r="V13">
-        <v>8.2309959000000002E-2</v>
+        <v>5.6815405999999999E-2</v>
       </c>
       <c r="W13">
         <v>28</v>
       </c>
       <c r="X13">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Y13">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="Z13">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>1.2865809000000001E-2</v>
+        <v>1.4156311E-2</v>
       </c>
       <c r="B14">
-        <v>1.10747663551401</v>
+        <v>1.06853582554517</v>
       </c>
       <c r="C14">
         <v>17.3333339691162</v>
@@ -1842,7 +1842,7 @@
         <v>12</v>
       </c>
       <c r="I14">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="J14">
         <v>7</v>
@@ -1854,34 +1854,34 @@
         <v>41</v>
       </c>
       <c r="M14">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="N14">
-        <v>711</v>
+        <v>686</v>
       </c>
       <c r="O14">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="P14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q14">
         <v>1</v>
       </c>
       <c r="R14">
-        <v>13.161991</v>
+        <v>14.241925</v>
       </c>
       <c r="S14" t="s">
         <v>28</v>
       </c>
-      <c r="T14">
-        <v>2.4433300000000001E-4</v>
+      <c r="T14" s="1">
+        <v>4.1751000000000001E-5</v>
       </c>
       <c r="U14" t="s">
         <v>29</v>
       </c>
       <c r="V14">
-        <v>1.3109422000000001E-2</v>
+        <v>1.4197309999999999E-2</v>
       </c>
       <c r="W14">
         <v>18</v>
@@ -1890,7 +1890,7 @@
         <v>1</v>
       </c>
       <c r="Y14">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="Z14">
         <v>7</v>
@@ -1898,10 +1898,10 @@
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>1.21589319999999E-2</v>
+        <v>1.2371323E-2</v>
       </c>
       <c r="B15">
-        <v>1.4640522875816899</v>
+        <v>1.23529411764705</v>
       </c>
       <c r="C15">
         <v>14.800000190734799</v>
@@ -1922,25 +1922,25 @@
         <v>13</v>
       </c>
       <c r="I15">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="J15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L15" t="s">
         <v>42</v>
       </c>
       <c r="M15">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="N15">
-        <v>224</v>
+        <v>189</v>
       </c>
       <c r="O15">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="P15">
         <v>3</v>
@@ -1949,39 +1949,39 @@
         <v>1</v>
       </c>
       <c r="R15">
-        <v>12.358127</v>
+        <v>12.424761999999999</v>
       </c>
       <c r="S15" t="s">
         <v>28</v>
       </c>
-      <c r="T15">
-        <v>1.4719599999999999E-4</v>
+      <c r="T15" s="1">
+        <v>3.5689999999999999E-5</v>
       </c>
       <c r="U15" t="s">
         <v>29</v>
       </c>
       <c r="V15">
-        <v>1.2305495E-2</v>
+        <v>1.2406209E-2</v>
       </c>
       <c r="W15">
         <v>5</v>
       </c>
       <c r="X15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y15">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="Z15">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>1.2242510999999999E-2</v>
+        <v>1.1459679E-2</v>
       </c>
       <c r="B16">
-        <v>1.9710982658959499</v>
+        <v>1.0693641618497101</v>
       </c>
       <c r="C16">
         <v>16.799999237060501</v>
@@ -2002,55 +2002,55 @@
         <v>14</v>
       </c>
       <c r="I16">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="J16">
         <v>7</v>
       </c>
       <c r="K16">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L16" t="s">
         <v>43</v>
       </c>
       <c r="M16">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="N16">
-        <v>341</v>
+        <v>185</v>
       </c>
       <c r="O16">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q16">
         <v>1</v>
       </c>
       <c r="R16">
-        <v>12.540647</v>
+        <v>11.481875</v>
       </c>
       <c r="S16" t="s">
         <v>28</v>
       </c>
-      <c r="T16">
-        <v>2.80177E-4</v>
+      <c r="T16" s="1">
+        <v>7.2180000000000002E-6</v>
       </c>
       <c r="U16" t="s">
         <v>29</v>
       </c>
       <c r="V16">
-        <v>1.2522092E-2</v>
+        <v>1.1466171000000001E-2</v>
       </c>
       <c r="W16">
         <v>5</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Z16">
         <v>7</v>
@@ -2058,10 +2058,10 @@
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>1.5431565E-2</v>
+        <v>1.5068751999999999E-2</v>
       </c>
       <c r="B17">
-        <v>2.19756838905775</v>
+        <v>1.63981762917933</v>
       </c>
       <c r="C17">
         <v>15.949999809265099</v>
@@ -2073,7 +2073,7 @@
         <v>25</v>
       </c>
       <c r="F17">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="G17" t="s">
         <v>26</v>
@@ -2082,63 +2082,63 @@
         <v>15</v>
       </c>
       <c r="I17">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="J17">
-        <v>301</v>
+        <v>487</v>
       </c>
       <c r="K17">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="L17" t="s">
         <v>44</v>
       </c>
       <c r="M17">
-        <v>547</v>
+        <v>286</v>
       </c>
       <c r="N17">
-        <v>1446</v>
+        <v>1079</v>
       </c>
       <c r="O17">
-        <v>547</v>
+        <v>286</v>
       </c>
       <c r="P17">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="Q17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R17">
-        <v>19.213097999999999</v>
+        <v>16.687750000000001</v>
       </c>
       <c r="S17" t="s">
         <v>28</v>
       </c>
       <c r="T17">
-        <v>3.679847E-3</v>
+        <v>1.554836E-3</v>
       </c>
       <c r="U17" t="s">
         <v>29</v>
       </c>
       <c r="V17">
-        <v>1.9110848999999999E-2</v>
+        <v>1.6623063E-2</v>
       </c>
       <c r="W17">
         <v>20</v>
       </c>
       <c r="X17">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="Y17">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="Z17">
-        <v>301</v>
+        <v>487</v>
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>1.203719E-2</v>
+        <v>1.25242729999999E-2</v>
       </c>
       <c r="B18">
         <v>1.27868852459016</v>
@@ -2165,7 +2165,7 @@
         <v>41</v>
       </c>
       <c r="J18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K18">
         <v>3</v>
@@ -2189,19 +2189,19 @@
         <v>1</v>
       </c>
       <c r="R18">
-        <v>12.131640000000001</v>
+        <v>12.598998999999999</v>
       </c>
       <c r="S18" t="s">
         <v>28</v>
       </c>
       <c r="T18" s="1">
-        <v>6.6513000000000005E-5</v>
+        <v>5.5053999999999998E-5</v>
       </c>
       <c r="U18" t="s">
         <v>29</v>
       </c>
       <c r="V18">
-        <v>1.2102753000000001E-2</v>
+        <v>1.2578717E-2</v>
       </c>
       <c r="W18">
         <v>5</v>
@@ -2213,12 +2213,12 @@
         <v>36</v>
       </c>
       <c r="Z18">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>1.11262499999999E-2</v>
+        <v>1.1832512999999999E-2</v>
       </c>
       <c r="B19">
         <v>1.0254777070063601</v>
@@ -2269,19 +2269,19 @@
         <v>1</v>
       </c>
       <c r="R19">
-        <v>11.147493000000001</v>
+        <v>11.854569</v>
       </c>
       <c r="S19" t="s">
         <v>28</v>
       </c>
       <c r="T19" s="1">
-        <v>6.4219999999999997E-6</v>
+        <v>6.9110000000000004E-6</v>
       </c>
       <c r="U19" t="s">
         <v>29</v>
       </c>
       <c r="V19">
-        <v>1.1131993E-2</v>
+        <v>1.1838579E-2</v>
       </c>
       <c r="W19">
         <v>5</v>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>1.6931214E-2</v>
+        <v>1.7611887999999999E-2</v>
       </c>
       <c r="B20">
-        <v>2.7976190476190399</v>
+        <v>3.06481481481481</v>
       </c>
       <c r="C20">
         <v>15.25</v>
@@ -2313,7 +2313,7 @@
         <v>25</v>
       </c>
       <c r="F20">
-        <v>372</v>
+        <v>392</v>
       </c>
       <c r="G20" t="s">
         <v>26</v>
@@ -2322,63 +2322,63 @@
         <v>18</v>
       </c>
       <c r="I20">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="J20">
-        <v>372</v>
+        <v>507</v>
       </c>
       <c r="K20">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="L20" t="s">
         <v>47</v>
       </c>
       <c r="M20">
-        <v>865</v>
+        <v>1075</v>
       </c>
       <c r="N20">
-        <v>2115</v>
+        <v>2317</v>
       </c>
       <c r="O20">
-        <v>865</v>
+        <v>1075</v>
       </c>
       <c r="P20">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="Q20">
         <v>1</v>
       </c>
       <c r="R20">
-        <v>25.876415999999999</v>
+        <v>22.267569999999999</v>
       </c>
       <c r="S20" t="s">
         <v>28</v>
       </c>
       <c r="T20">
-        <v>8.8024750000000006E-3</v>
+        <v>4.4767670000000004E-3</v>
       </c>
       <c r="U20" t="s">
         <v>29</v>
       </c>
       <c r="V20">
-        <v>2.5733175E-2</v>
+        <v>2.2088100999999999E-2</v>
       </c>
       <c r="W20">
         <v>24</v>
       </c>
       <c r="X20">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Y20">
         <v>4</v>
       </c>
       <c r="Z20">
-        <v>372</v>
+        <v>507</v>
       </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>1.1420236E-2</v>
+        <v>1.193988E-2</v>
       </c>
       <c r="B21">
         <v>1.02877697841726</v>
@@ -2402,7 +2402,7 @@
         <v>19</v>
       </c>
       <c r="I21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J21">
         <v>6</v>
@@ -2423,25 +2423,25 @@
         <v>0</v>
       </c>
       <c r="P21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q21">
         <v>1</v>
       </c>
       <c r="R21">
-        <v>11.453982</v>
+        <v>11.964226</v>
       </c>
       <c r="S21" t="s">
         <v>28</v>
       </c>
       <c r="T21" s="1">
-        <v>1.7419E-5</v>
+        <v>6.8090000000000004E-6</v>
       </c>
       <c r="U21" t="s">
         <v>29</v>
       </c>
       <c r="V21">
-        <v>1.1436665E-2</v>
+        <v>1.1945971E-2</v>
       </c>
       <c r="W21">
         <v>5</v>
@@ -2458,10 +2458,10 @@
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>1.3314695E-2</v>
+        <v>1.2824907E-2</v>
       </c>
       <c r="B22">
-        <v>2.50761421319796</v>
+        <v>2.2741116751269002</v>
       </c>
       <c r="C22">
         <v>13.571428298950099</v>
@@ -2473,7 +2473,7 @@
         <v>25</v>
       </c>
       <c r="F22">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G22" t="s">
         <v>26</v>
@@ -2482,66 +2482,66 @@
         <v>20</v>
       </c>
       <c r="I22">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="J22">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="K22">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L22" t="s">
         <v>49</v>
       </c>
       <c r="M22">
-        <v>254</v>
+        <v>184</v>
       </c>
       <c r="N22">
-        <v>494</v>
+        <v>448</v>
       </c>
       <c r="O22">
-        <v>254</v>
+        <v>184</v>
       </c>
       <c r="P22">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q22">
         <v>1</v>
       </c>
       <c r="R22">
-        <v>14.129155000000001</v>
+        <v>13.134884</v>
       </c>
       <c r="S22" t="s">
         <v>28</v>
       </c>
       <c r="T22">
-        <v>7.9195100000000005E-4</v>
+        <v>2.8218600000000003E-4</v>
       </c>
       <c r="U22" t="s">
         <v>29</v>
       </c>
       <c r="V22">
-        <v>1.4106138000000001E-2</v>
+        <v>1.3106342999999999E-2</v>
       </c>
       <c r="W22">
         <v>7</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Y22">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="Z22">
-        <v>35</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>1.26810779999999E-2</v>
+        <v>1.3608248999999999E-2</v>
       </c>
       <c r="B23">
-        <v>3.0263157894736801</v>
+        <v>2.7631578947368398</v>
       </c>
       <c r="C23">
         <v>11.375</v>
@@ -2553,7 +2553,7 @@
         <v>25</v>
       </c>
       <c r="F23">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="G23" t="s">
         <v>26</v>
@@ -2562,66 +2562,66 @@
         <v>21</v>
       </c>
       <c r="I23">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="J23">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="K23">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L23" t="s">
         <v>50</v>
       </c>
       <c r="M23">
-        <v>306</v>
+        <v>242</v>
       </c>
       <c r="N23">
-        <v>575</v>
+        <v>525</v>
       </c>
       <c r="O23">
-        <v>306</v>
+        <v>242</v>
       </c>
       <c r="P23">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q23">
         <v>1</v>
       </c>
       <c r="R23">
-        <v>13.535507000000001</v>
+        <v>14.262233999999999</v>
       </c>
       <c r="S23" t="s">
         <v>28</v>
       </c>
       <c r="T23">
-        <v>8.2963100000000005E-4</v>
+        <v>6.2292599999999999E-4</v>
       </c>
       <c r="U23" t="s">
         <v>29</v>
       </c>
       <c r="V23">
-        <v>1.3510269E-2</v>
+        <v>1.423049E-2</v>
       </c>
       <c r="W23">
         <v>8</v>
       </c>
       <c r="X23">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y23">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="Z23">
-        <v>34</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>1.5856677999999999E-2</v>
+        <v>2.0495024000000001E-2</v>
       </c>
       <c r="B24">
-        <v>2.5094339622641502</v>
+        <v>2.4238993710691799</v>
       </c>
       <c r="C24">
         <v>15.399999618530201</v>
@@ -2633,7 +2633,7 @@
         <v>25</v>
       </c>
       <c r="F24">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="G24" t="s">
         <v>26</v>
@@ -2642,66 +2642,66 @@
         <v>22</v>
       </c>
       <c r="I24">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="J24">
-        <v>425</v>
+        <v>497</v>
       </c>
       <c r="K24">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="L24" t="s">
         <v>51</v>
       </c>
       <c r="M24">
-        <v>855</v>
+        <v>815</v>
       </c>
       <c r="N24">
-        <v>1995</v>
+        <v>1927</v>
       </c>
       <c r="O24">
-        <v>855</v>
+        <v>815</v>
       </c>
       <c r="P24">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="Q24">
         <v>1</v>
       </c>
       <c r="R24">
-        <v>25.726562999999999</v>
+        <v>27.869489000000002</v>
       </c>
       <c r="S24" t="s">
         <v>28</v>
       </c>
       <c r="T24">
-        <v>9.7286520000000008E-3</v>
+        <v>7.1781809999999996E-3</v>
       </c>
       <c r="U24" t="s">
         <v>29</v>
       </c>
       <c r="V24">
-        <v>2.5584834000000001E-2</v>
+        <v>2.7672492E-2</v>
       </c>
       <c r="W24">
         <v>25</v>
       </c>
       <c r="X24">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="Y24">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="Z24">
-        <v>425</v>
+        <v>497</v>
       </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>1.2360659E-2</v>
+        <v>1.2249593E-2</v>
       </c>
       <c r="B25">
-        <v>1.31196581196581</v>
+        <v>1.02564102564102</v>
       </c>
       <c r="C25">
         <v>16.214284896850501</v>
@@ -2722,55 +2722,55 @@
         <v>23</v>
       </c>
       <c r="I25">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="J25">
         <v>6</v>
       </c>
       <c r="K25">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L25" t="s">
         <v>52</v>
       </c>
       <c r="M25">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="N25">
-        <v>614</v>
+        <v>480</v>
       </c>
       <c r="O25">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="P25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q25">
         <v>1</v>
       </c>
       <c r="R25">
-        <v>12.550884</v>
+        <v>12.310005</v>
       </c>
       <c r="S25" t="s">
         <v>28</v>
       </c>
-      <c r="T25">
-        <v>1.6426099999999999E-4</v>
+      <c r="T25" s="1">
+        <v>7.9840000000000001E-6</v>
       </c>
       <c r="U25" t="s">
         <v>29</v>
       </c>
       <c r="V25">
-        <v>1.2524329000000001E-2</v>
+        <v>1.2256938E-2</v>
       </c>
       <c r="W25">
         <v>14</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Y25">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Z25">
         <v>6</v>
@@ -2778,10 +2778,10 @@
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>3.1086424000000001E-2</v>
+        <v>4.5369413999999997E-2</v>
       </c>
       <c r="B26">
-        <v>3.4352373290426299</v>
+        <v>3.7119871279163301</v>
       </c>
       <c r="C26">
         <v>20.931034088134702</v>
@@ -2802,7 +2802,7 @@
         <v>24</v>
       </c>
       <c r="I26">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="J26">
         <v>63</v>
@@ -2814,13 +2814,13 @@
         <v>53</v>
       </c>
       <c r="M26">
-        <v>2290</v>
+        <v>2571</v>
       </c>
       <c r="N26">
-        <v>4270</v>
+        <v>4614</v>
       </c>
       <c r="O26">
-        <v>2290</v>
+        <v>2571</v>
       </c>
       <c r="P26">
         <v>27</v>
@@ -2829,28 +2829,28 @@
         <v>1</v>
       </c>
       <c r="R26">
-        <v>172.22125600000001</v>
+        <v>211.35485199999999</v>
       </c>
       <c r="S26" t="s">
         <v>28</v>
       </c>
       <c r="T26">
-        <v>0.14090069599999999</v>
+        <v>0.16569720700000001</v>
       </c>
       <c r="U26" t="s">
         <v>29</v>
       </c>
       <c r="V26">
-        <v>0.17198658</v>
+        <v>0.21106607999999999</v>
       </c>
       <c r="W26">
         <v>29</v>
       </c>
       <c r="X26">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z26">
         <v>63</v>
@@ -2858,10 +2858,10 @@
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>2.90916629999999E-2</v>
+        <v>4.5587830999999898E-2</v>
       </c>
       <c r="B27">
-        <v>4.0574358974358899</v>
+        <v>5.1210256410256401</v>
       </c>
       <c r="C27">
         <v>19</v>
@@ -2873,7 +2873,7 @@
         <v>33</v>
       </c>
       <c r="F27">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="G27" t="s">
         <v>26</v>
@@ -2882,66 +2882,66 @@
         <v>25</v>
       </c>
       <c r="I27">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="J27">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="K27">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="L27" t="s">
         <v>54</v>
       </c>
       <c r="M27">
-        <v>2252</v>
+        <v>3050</v>
       </c>
       <c r="N27">
-        <v>3956</v>
+        <v>4993</v>
       </c>
       <c r="O27">
-        <v>2252</v>
+        <v>3050</v>
       </c>
       <c r="P27">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="Q27">
         <v>1</v>
       </c>
       <c r="R27">
-        <v>621.56693700000005</v>
+        <v>98.735713000000004</v>
       </c>
       <c r="S27" t="s">
         <v>28</v>
       </c>
       <c r="T27">
-        <v>0.59221603300000003</v>
+        <v>5.2824358000000002E-2</v>
       </c>
       <c r="U27" t="s">
         <v>29</v>
       </c>
       <c r="V27">
-        <v>0.62130716900000005</v>
+        <v>9.8411581999999997E-2</v>
       </c>
       <c r="W27">
         <v>25</v>
       </c>
       <c r="X27">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="Y27">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="Z27">
-        <v>52</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>1.7039289999999901E-2</v>
+        <v>2.4727804999999999E-2</v>
       </c>
       <c r="B28">
-        <v>3.1352459016393399</v>
+        <v>3.5245901639344202</v>
       </c>
       <c r="C28">
         <v>22.375</v>
@@ -2953,7 +2953,7 @@
         <v>33</v>
       </c>
       <c r="F28">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G28" t="s">
         <v>26</v>
@@ -2962,66 +2962,66 @@
         <v>26</v>
       </c>
       <c r="I28">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="J28">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="K28">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L28" t="s">
         <v>55</v>
       </c>
       <c r="M28">
-        <v>1219</v>
+        <v>1458</v>
       </c>
       <c r="N28">
-        <v>2295</v>
+        <v>2580</v>
       </c>
       <c r="O28">
-        <v>1219</v>
+        <v>1458</v>
       </c>
       <c r="P28">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Q28">
         <v>1</v>
       </c>
       <c r="R28">
-        <v>35.409934999999997</v>
+        <v>39.212808000000003</v>
       </c>
       <c r="S28" t="s">
         <v>28</v>
       </c>
       <c r="T28">
-        <v>1.8238473000000002E-2</v>
+        <v>1.4298724000000001E-2</v>
       </c>
       <c r="U28" t="s">
         <v>29</v>
       </c>
       <c r="V28">
-        <v>3.5277258999999998E-2</v>
+        <v>3.902593E-2</v>
       </c>
       <c r="W28">
         <v>16</v>
       </c>
       <c r="X28">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="Y28">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="Z28">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>1.7836925E-2</v>
+        <v>1.7501315999999999E-2</v>
       </c>
       <c r="B29">
-        <v>2.9510869565217299</v>
+        <v>2.72101449275362</v>
       </c>
       <c r="C29">
         <v>19.214284896850501</v>
@@ -3033,7 +3033,7 @@
         <v>33</v>
       </c>
       <c r="F29">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G29" t="s">
         <v>26</v>
@@ -3042,10 +3042,10 @@
         <v>27</v>
       </c>
       <c r="I29">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J29">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="K29">
         <v>13</v>
@@ -3054,54 +3054,54 @@
         <v>56</v>
       </c>
       <c r="M29">
-        <v>874</v>
+        <v>764</v>
       </c>
       <c r="N29">
-        <v>1629</v>
+        <v>1502</v>
       </c>
       <c r="O29">
-        <v>874</v>
+        <v>764</v>
       </c>
       <c r="P29">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Q29">
         <v>1</v>
       </c>
       <c r="R29">
-        <v>23.074093000000001</v>
+        <v>20.852425</v>
       </c>
       <c r="S29" t="s">
         <v>28</v>
       </c>
       <c r="T29">
-        <v>5.1283869999999999E-3</v>
+        <v>3.2834269999999998E-3</v>
       </c>
       <c r="U29" t="s">
         <v>29</v>
       </c>
       <c r="V29">
-        <v>2.2964741E-2</v>
+        <v>2.0784112E-2</v>
       </c>
       <c r="W29">
         <v>14</v>
       </c>
       <c r="X29">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="Y29">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="Z29">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>1.3760150000000001E-2</v>
+        <v>1.551875E-2</v>
       </c>
       <c r="B30">
-        <v>1.9978902953586399</v>
+        <v>2.1603375527426101</v>
       </c>
       <c r="C30">
         <v>19.25</v>
@@ -3113,7 +3113,7 @@
         <v>33</v>
       </c>
       <c r="F30">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G30" t="s">
         <v>26</v>
@@ -3122,66 +3122,66 @@
         <v>28</v>
       </c>
       <c r="I30">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="J30">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="K30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L30" t="s">
         <v>57</v>
       </c>
       <c r="M30">
-        <v>371</v>
+        <v>429</v>
       </c>
       <c r="N30">
-        <v>947</v>
+        <v>1024</v>
       </c>
       <c r="O30">
-        <v>371</v>
+        <v>429</v>
       </c>
       <c r="P30">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="Q30">
         <v>1</v>
       </c>
       <c r="R30">
-        <v>15.931150000000001</v>
+        <v>17.561313999999999</v>
       </c>
       <c r="S30" t="s">
         <v>28</v>
       </c>
       <c r="T30">
-        <v>2.1093919999999999E-3</v>
+        <v>1.9943349999999999E-3</v>
       </c>
       <c r="U30" t="s">
         <v>29</v>
       </c>
       <c r="V30">
-        <v>1.5869131000000002E-2</v>
+        <v>1.7512519000000001E-2</v>
       </c>
       <c r="W30">
         <v>12</v>
       </c>
       <c r="X30">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y30">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="Z30">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>1.27055609999999E-2</v>
+        <v>1.4145941E-2</v>
       </c>
       <c r="B31">
-        <v>2.1960784313725399</v>
+        <v>1.8496732026143701</v>
       </c>
       <c r="C31">
         <v>18.625</v>
@@ -3193,7 +3193,7 @@
         <v>33</v>
       </c>
       <c r="F31">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G31" t="s">
         <v>26</v>
@@ -3202,66 +3202,66 @@
         <v>29</v>
       </c>
       <c r="I31">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="J31">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K31">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L31" t="s">
         <v>58</v>
       </c>
       <c r="M31">
-        <v>288</v>
+        <v>204</v>
       </c>
       <c r="N31">
-        <v>672</v>
+        <v>566</v>
       </c>
       <c r="O31">
-        <v>288</v>
+        <v>204</v>
       </c>
       <c r="P31">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q31">
         <v>1</v>
       </c>
       <c r="R31">
-        <v>13.356173</v>
+        <v>14.643801</v>
       </c>
       <c r="S31" t="s">
         <v>28</v>
       </c>
       <c r="T31">
-        <v>6.2302600000000005E-4</v>
+        <v>4.70762E-4</v>
       </c>
       <c r="U31" t="s">
         <v>29</v>
       </c>
       <c r="V31">
-        <v>1.3328059E-2</v>
+        <v>1.4616214000000001E-2</v>
       </c>
       <c r="W31">
         <v>8</v>
       </c>
       <c r="X31">
+        <v>8</v>
+      </c>
+      <c r="Y31">
+        <v>55</v>
+      </c>
+      <c r="Z31">
         <v>15</v>
-      </c>
-      <c r="Y31">
-        <v>29</v>
-      </c>
-      <c r="Z31">
-        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>1.2862634E-2</v>
+        <v>1.4148506999999999E-2</v>
       </c>
       <c r="B32">
-        <v>2.37619047619047</v>
+        <v>2.4619047619047598</v>
       </c>
       <c r="C32">
         <v>12.625</v>
@@ -3273,7 +3273,7 @@
         <v>33</v>
       </c>
       <c r="F32">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G32" t="s">
         <v>26</v>
@@ -3282,10 +3282,10 @@
         <v>30</v>
       </c>
       <c r="I32">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="J32">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K32">
         <v>7</v>
@@ -3294,54 +3294,54 @@
         <v>59</v>
       </c>
       <c r="M32">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="N32">
-        <v>499</v>
+        <v>517</v>
       </c>
       <c r="O32">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="P32">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q32">
         <v>1</v>
       </c>
       <c r="R32">
-        <v>13.872033</v>
+        <v>15.042593999999999</v>
       </c>
       <c r="S32" t="s">
         <v>28</v>
       </c>
       <c r="T32">
-        <v>9.8368700000000002E-4</v>
+        <v>8.5961800000000004E-4</v>
       </c>
       <c r="U32" t="s">
         <v>29</v>
       </c>
       <c r="V32">
-        <v>1.3845787999999999E-2</v>
+        <v>1.500749E-2</v>
       </c>
       <c r="W32">
         <v>8</v>
       </c>
       <c r="X32">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Y32">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="Z32">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>8.3087715999994302E-2</v>
+        <v>0.15120546100000001</v>
       </c>
       <c r="B33">
-        <v>15.577656675749299</v>
+        <v>18.772933696639399</v>
       </c>
       <c r="C33">
         <v>19.888889312744102</v>
@@ -3352,6 +3352,9 @@
       <c r="E33">
         <v>33</v>
       </c>
+      <c r="F33">
+        <v>232</v>
+      </c>
       <c r="G33" t="s">
         <v>26</v>
       </c>
@@ -3359,66 +3362,66 @@
         <v>31</v>
       </c>
       <c r="I33">
-        <v>262</v>
+        <v>375</v>
       </c>
       <c r="J33">
-        <v>159</v>
+        <v>232</v>
       </c>
       <c r="K33">
-        <v>83</v>
+        <v>201</v>
       </c>
       <c r="L33" t="s">
         <v>60</v>
       </c>
       <c r="M33">
-        <v>11341</v>
+        <v>16326</v>
       </c>
       <c r="N33">
-        <v>17151</v>
+        <v>20669</v>
       </c>
       <c r="O33">
-        <v>11341</v>
+        <v>16326</v>
       </c>
       <c r="P33">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="Q33">
         <v>1</v>
       </c>
       <c r="R33">
-        <v>124325.28357499999</v>
+        <v>1565.498341</v>
       </c>
       <c r="S33" t="s">
         <v>28</v>
       </c>
       <c r="T33">
-        <v>124.242196413</v>
+        <v>1.4126010339999999</v>
       </c>
       <c r="U33" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="V33">
-        <v>124.325283575</v>
+        <v>1.5638059630000001</v>
       </c>
       <c r="W33">
         <v>27</v>
       </c>
       <c r="X33">
-        <v>182</v>
+        <v>321</v>
       </c>
       <c r="Y33">
         <v>0</v>
       </c>
       <c r="Z33">
-        <v>177</v>
+        <v>232</v>
       </c>
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>3.0146072999999898E-2</v>
+        <v>5.1673889000000001E-2</v>
       </c>
       <c r="B34">
-        <v>4.5279805352798004</v>
+        <v>5.5486618004866104</v>
       </c>
       <c r="C34">
         <v>20.049999237060501</v>
@@ -3430,7 +3433,7 @@
         <v>33</v>
       </c>
       <c r="F34">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G34" t="s">
         <v>26</v>
@@ -3439,66 +3442,66 @@
         <v>32</v>
       </c>
       <c r="I34">
-        <v>178</v>
+        <v>212</v>
       </c>
       <c r="J34">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="K34">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="L34" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M34">
-        <v>2207</v>
+        <v>2887</v>
       </c>
       <c r="N34">
-        <v>3722</v>
+        <v>4561</v>
       </c>
       <c r="O34">
-        <v>2207</v>
+        <v>2887</v>
       </c>
       <c r="P34">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="Q34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R34">
-        <v>499.57542000000001</v>
+        <v>112.354364</v>
       </c>
       <c r="S34" t="s">
         <v>28</v>
       </c>
       <c r="T34">
-        <v>0.46908782700000001</v>
+        <v>6.0381236999999997E-2</v>
       </c>
       <c r="U34" t="s">
         <v>29</v>
       </c>
       <c r="V34">
-        <v>0.499233388</v>
+        <v>0.112054499</v>
       </c>
       <c r="W34">
         <v>20</v>
       </c>
       <c r="X34">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="Y34">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="Z34">
-        <v>46</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>1.39776349999999E-2</v>
+        <v>2.0730386E-2</v>
       </c>
       <c r="B35">
-        <v>2.0267716535433</v>
+        <v>3.3779527559055098</v>
       </c>
       <c r="C35">
         <v>18.176469802856399</v>
@@ -3510,7 +3513,7 @@
         <v>33</v>
       </c>
       <c r="F35">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G35" t="s">
         <v>26</v>
@@ -3519,66 +3522,66 @@
         <v>33</v>
       </c>
       <c r="I35">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="J35">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="K35">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="L35" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M35">
-        <v>486</v>
+        <v>1186</v>
       </c>
       <c r="N35">
-        <v>1287</v>
+        <v>2145</v>
       </c>
       <c r="O35">
-        <v>486</v>
+        <v>1186</v>
       </c>
       <c r="P35">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Q35">
         <v>1</v>
       </c>
       <c r="R35">
-        <v>16.016887000000001</v>
+        <v>29.501355</v>
       </c>
       <c r="S35" t="s">
         <v>28</v>
       </c>
       <c r="T35">
-        <v>1.9817379999999998E-3</v>
+        <v>8.6072960000000004E-3</v>
       </c>
       <c r="U35" t="s">
         <v>29</v>
       </c>
       <c r="V35">
-        <v>1.5958857999999999E-2</v>
+        <v>2.9337185000000002E-2</v>
       </c>
       <c r="W35">
         <v>17</v>
       </c>
       <c r="X35">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="Y35">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="Z35">
-        <v>33</v>
+        <v>63</v>
       </c>
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>6.8111182999999104E-2</v>
+        <v>1.49384217799999</v>
       </c>
       <c r="B36">
-        <v>13.4716516023007</v>
+        <v>86.713229252259595</v>
       </c>
       <c r="C36">
         <v>20.482759475708001</v>
@@ -3596,52 +3599,52 @@
         <v>34</v>
       </c>
       <c r="I36">
-        <v>188</v>
+        <v>1715</v>
       </c>
       <c r="J36">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="K36">
-        <v>163</v>
+        <v>1241</v>
       </c>
       <c r="L36" t="s">
+        <v>63</v>
+      </c>
+      <c r="M36">
+        <v>216202</v>
+      </c>
+      <c r="N36">
+        <v>105530</v>
+      </c>
+      <c r="O36">
+        <v>216202</v>
+      </c>
+      <c r="P36">
+        <v>16</v>
+      </c>
+      <c r="Q36">
+        <v>1</v>
+      </c>
+      <c r="R36">
+        <v>120014.85902</v>
+      </c>
+      <c r="S36" t="s">
+        <v>28</v>
+      </c>
+      <c r="T36">
+        <v>118.521018493</v>
+      </c>
+      <c r="U36" t="s">
         <v>64</v>
       </c>
-      <c r="M36">
-        <v>9515</v>
-      </c>
-      <c r="N36">
-        <v>16395</v>
-      </c>
-      <c r="O36">
-        <v>9515</v>
-      </c>
-      <c r="P36">
-        <v>84</v>
-      </c>
-      <c r="Q36">
-        <v>1</v>
-      </c>
-      <c r="R36">
-        <v>120866.666796</v>
-      </c>
-      <c r="S36" t="s">
-        <v>28</v>
-      </c>
-      <c r="T36">
-        <v>120.79855626</v>
-      </c>
-      <c r="U36" t="s">
-        <v>61</v>
-      </c>
       <c r="V36">
-        <v>120.866666796</v>
+        <v>120.01485902</v>
       </c>
       <c r="W36">
         <v>29</v>
       </c>
       <c r="X36">
-        <v>102</v>
+        <v>1697</v>
       </c>
       <c r="Y36">
         <v>0</v>
@@ -3652,10 +3655,10 @@
     </row>
     <row r="37" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>6.9353144999993704E-2</v>
+        <v>1.54252698200001</v>
       </c>
       <c r="B37">
-        <v>14.2451768488745</v>
+        <v>81.284565916398705</v>
       </c>
       <c r="C37">
         <v>21.714284896850501</v>
@@ -3673,66 +3676,66 @@
         <v>35</v>
       </c>
       <c r="I37">
-        <v>193</v>
+        <v>1636</v>
       </c>
       <c r="J37">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="K37">
-        <v>163</v>
+        <v>1084</v>
       </c>
       <c r="L37" t="s">
         <v>65</v>
       </c>
       <c r="M37">
-        <v>10664</v>
+        <v>198429</v>
       </c>
       <c r="N37">
-        <v>17721</v>
+        <v>101118</v>
       </c>
       <c r="O37">
-        <v>10664</v>
+        <v>198429</v>
       </c>
       <c r="P37">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="Q37">
         <v>1</v>
       </c>
       <c r="R37">
-        <v>120762.592884</v>
+        <v>120270.41294900001</v>
       </c>
       <c r="S37" t="s">
         <v>28</v>
       </c>
       <c r="T37">
-        <v>120.693240531</v>
+        <v>118.72788688599999</v>
       </c>
       <c r="U37" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="V37">
-        <v>120.762592884</v>
+        <v>120.270412949</v>
       </c>
       <c r="W37">
         <v>28</v>
       </c>
       <c r="X37">
-        <v>99</v>
+        <v>1624</v>
       </c>
       <c r="Y37">
         <v>0</v>
       </c>
       <c r="Z37">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="38" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>1.5092012E-2</v>
+        <v>1.4949267999999899E-2</v>
       </c>
       <c r="B38">
-        <v>2.4267912772585598</v>
+        <v>2.2788161993769398</v>
       </c>
       <c r="C38">
         <v>17.3333339691162</v>
@@ -3753,55 +3756,55 @@
         <v>36</v>
       </c>
       <c r="I38">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="J38">
         <v>15</v>
       </c>
       <c r="K38">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L38" t="s">
         <v>66</v>
       </c>
       <c r="M38">
-        <v>713</v>
+        <v>641</v>
       </c>
       <c r="N38">
-        <v>1558</v>
+        <v>1463</v>
       </c>
       <c r="O38">
-        <v>713</v>
+        <v>641</v>
       </c>
       <c r="P38">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Q38">
         <v>1</v>
       </c>
       <c r="R38">
-        <v>20.528737</v>
+        <v>16.191009999999999</v>
       </c>
       <c r="S38" t="s">
         <v>28</v>
       </c>
       <c r="T38">
-        <v>5.3442669999999998E-3</v>
+        <v>1.1708700000000001E-3</v>
       </c>
       <c r="U38" t="s">
         <v>29</v>
       </c>
       <c r="V38">
-        <v>2.0435702E-2</v>
+        <v>1.6119443000000001E-2</v>
       </c>
       <c r="W38">
         <v>18</v>
       </c>
       <c r="X38">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="Y38">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z38">
         <v>15</v>
@@ -3809,10 +3812,10 @@
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>1.2478411E-2</v>
+        <v>1.3290378E-2</v>
       </c>
       <c r="B39">
-        <v>1.8039215686274499</v>
+        <v>2.3267973856209099</v>
       </c>
       <c r="C39">
         <v>14.800000190734799</v>
@@ -3833,10 +3836,10 @@
         <v>37</v>
       </c>
       <c r="I39">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="J39">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K39">
         <v>5</v>
@@ -3845,54 +3848,54 @@
         <v>67</v>
       </c>
       <c r="M39">
-        <v>94</v>
+        <v>152</v>
       </c>
       <c r="N39">
-        <v>276</v>
+        <v>356</v>
       </c>
       <c r="O39">
-        <v>94</v>
+        <v>152</v>
       </c>
       <c r="P39">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Q39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R39">
-        <v>13.225930999999999</v>
+        <v>14.211214999999999</v>
       </c>
       <c r="S39" t="s">
         <v>28</v>
       </c>
       <c r="T39">
-        <v>7.1958899999999997E-4</v>
+        <v>8.5739699999999998E-4</v>
       </c>
       <c r="U39" t="s">
         <v>29</v>
       </c>
       <c r="V39">
-        <v>1.3197462E-2</v>
+        <v>1.4147221999999999E-2</v>
       </c>
       <c r="W39">
         <v>5</v>
       </c>
       <c r="X39">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y39">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="Z39">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>1.2638916E-2</v>
+        <v>1.3742766999999999E-2</v>
       </c>
       <c r="B40">
-        <v>2.67630057803468</v>
+        <v>2.7398843930635799</v>
       </c>
       <c r="C40">
         <v>16.799999237060501</v>
@@ -3913,10 +3916,10 @@
         <v>38</v>
       </c>
       <c r="I40">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="J40">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K40">
         <v>8</v>
@@ -3925,13 +3928,13 @@
         <v>68</v>
       </c>
       <c r="M40">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="N40">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="O40">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="P40">
         <v>3</v>
@@ -3940,39 +3943,39 @@
         <v>1</v>
       </c>
       <c r="R40">
-        <v>13.054245999999999</v>
+        <v>14.318894999999999</v>
       </c>
       <c r="S40" t="s">
         <v>28</v>
       </c>
       <c r="T40">
-        <v>3.9250199999999998E-4</v>
+        <v>5.5117700000000003E-4</v>
       </c>
       <c r="U40" t="s">
         <v>29</v>
       </c>
       <c r="V40">
-        <v>1.3030952E-2</v>
+        <v>1.4293401000000001E-2</v>
       </c>
       <c r="W40">
         <v>5</v>
       </c>
       <c r="X40">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y40">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="Z40">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>1.8562011999999899E-2</v>
+        <v>2.3618574999999999E-2</v>
       </c>
       <c r="B41">
-        <v>3.9772036474164101</v>
+        <v>3.7720364741641301</v>
       </c>
       <c r="C41">
         <v>15.949999809265099</v>
@@ -3984,7 +3987,7 @@
         <v>25</v>
       </c>
       <c r="F41">
-        <v>345</v>
+        <v>382</v>
       </c>
       <c r="G41" t="s">
         <v>26</v>
@@ -3993,66 +3996,66 @@
         <v>39</v>
       </c>
       <c r="I41">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="J41">
-        <v>345</v>
+        <v>506</v>
       </c>
       <c r="K41">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="L41" t="s">
         <v>69</v>
       </c>
       <c r="M41">
-        <v>1434</v>
+        <v>1415</v>
       </c>
       <c r="N41">
-        <v>2617</v>
+        <v>2482</v>
       </c>
       <c r="O41">
-        <v>1434</v>
+        <v>1415</v>
       </c>
       <c r="P41">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="Q41">
         <v>1</v>
       </c>
       <c r="R41">
-        <v>51.684407</v>
+        <v>39.735095999999999</v>
       </c>
       <c r="S41" t="s">
         <v>28</v>
       </c>
       <c r="T41">
-        <v>3.2930656000000003E-2</v>
+        <v>1.5893922000000001E-2</v>
       </c>
       <c r="U41" t="s">
         <v>29</v>
       </c>
       <c r="V41">
-        <v>5.1492081000000002E-2</v>
+        <v>3.9511873000000003E-2</v>
       </c>
       <c r="W41">
         <v>20</v>
       </c>
       <c r="X41">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="Y41">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="Z41">
-        <v>345</v>
+        <v>506</v>
       </c>
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>1.4246839000000001E-2</v>
+        <v>1.5438231E-2</v>
       </c>
       <c r="B42">
-        <v>3.7540983606557301</v>
+        <v>4.10928961748633</v>
       </c>
       <c r="C42">
         <v>17.799999237060501</v>
@@ -4064,7 +4067,7 @@
         <v>25</v>
       </c>
       <c r="F42">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G42" t="s">
         <v>26</v>
@@ -4073,66 +4076,66 @@
         <v>40</v>
       </c>
       <c r="I42">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="J42">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K42">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L42" t="s">
         <v>70</v>
       </c>
       <c r="M42">
-        <v>403</v>
+        <v>451</v>
       </c>
       <c r="N42">
-        <v>687</v>
+        <v>752</v>
       </c>
       <c r="O42">
-        <v>403</v>
+        <v>451</v>
       </c>
       <c r="P42">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R42">
-        <v>16.722190000000001</v>
+        <v>20.487791000000001</v>
       </c>
       <c r="S42" t="s">
         <v>28</v>
       </c>
       <c r="T42">
-        <v>2.4403990000000002E-3</v>
+        <v>4.9217530000000001E-3</v>
       </c>
       <c r="U42" t="s">
         <v>29</v>
       </c>
       <c r="V42">
-        <v>1.6686596000000001E-2</v>
+        <v>2.0359400999999999E-2</v>
       </c>
       <c r="W42">
         <v>5</v>
       </c>
       <c r="X42">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="Y42">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="Z42">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>1.1826428E-2</v>
+        <v>1.2361934E-2</v>
       </c>
       <c r="B43">
-        <v>1.5159235668789801</v>
+        <v>1.73248407643312</v>
       </c>
       <c r="C43">
         <v>15.199999809265099</v>
@@ -4153,10 +4156,10 @@
         <v>41</v>
       </c>
       <c r="I43">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="J43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K43">
         <v>4</v>
@@ -4165,13 +4168,13 @@
         <v>71</v>
       </c>
       <c r="M43">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="N43">
-        <v>238</v>
+        <v>272</v>
       </c>
       <c r="O43">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="P43">
         <v>2</v>
@@ -4180,19 +4183,19 @@
         <v>1</v>
       </c>
       <c r="R43">
-        <v>11.916899000000001</v>
+        <v>12.507432</v>
       </c>
       <c r="S43" t="s">
         <v>28</v>
       </c>
-      <c r="T43" s="1">
-        <v>7.3918000000000006E-5</v>
+      <c r="T43">
+        <v>1.1523600000000001E-4</v>
       </c>
       <c r="U43" t="s">
         <v>29</v>
       </c>
       <c r="V43">
-        <v>1.1899728E-2</v>
+        <v>1.2476556E-2</v>
       </c>
       <c r="W43">
         <v>5</v>
@@ -4201,18 +4204,18 @@
         <v>2</v>
       </c>
       <c r="Y43">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="Z43">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>1.672384E-2</v>
+        <v>1.9491994999999901E-2</v>
       </c>
       <c r="B44">
-        <v>2.7645502645502602</v>
+        <v>2.91534391534391</v>
       </c>
       <c r="C44">
         <v>15.25</v>
@@ -4224,7 +4227,7 @@
         <v>25</v>
       </c>
       <c r="F44">
-        <v>323</v>
+        <v>346</v>
       </c>
       <c r="G44" t="s">
         <v>26</v>
@@ -4233,66 +4236,66 @@
         <v>42</v>
       </c>
       <c r="I44">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="J44">
-        <v>323</v>
+        <v>473</v>
       </c>
       <c r="K44">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L44" t="s">
         <v>72</v>
       </c>
       <c r="M44">
-        <v>930</v>
+        <v>1054</v>
       </c>
       <c r="N44">
-        <v>2090</v>
+        <v>2204</v>
       </c>
       <c r="O44">
-        <v>930</v>
+        <v>1054</v>
       </c>
       <c r="P44">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="Q44">
         <v>1</v>
       </c>
       <c r="R44">
-        <v>49.919231000000003</v>
+        <v>26.805053000000001</v>
       </c>
       <c r="S44" t="s">
         <v>28</v>
       </c>
       <c r="T44">
-        <v>3.3027714999999999E-2</v>
+        <v>7.1007459999999998E-3</v>
       </c>
       <c r="U44" t="s">
         <v>29</v>
       </c>
       <c r="V44">
-        <v>4.9751016000000002E-2</v>
+        <v>2.6592246E-2</v>
       </c>
       <c r="W44">
         <v>24</v>
       </c>
       <c r="X44">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z44">
-        <v>323</v>
+        <v>473</v>
       </c>
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>1.2127979000000001E-2</v>
+        <v>1.3929819E-2</v>
       </c>
       <c r="B45">
-        <v>1.86330935251798</v>
+        <v>1.7697841726618699</v>
       </c>
       <c r="C45">
         <v>13.399999618530201</v>
@@ -4304,7 +4307,7 @@
         <v>25</v>
       </c>
       <c r="F45">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G45" t="s">
         <v>26</v>
@@ -4313,66 +4316,66 @@
         <v>43</v>
       </c>
       <c r="I45">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="J45">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L45" t="s">
         <v>73</v>
       </c>
       <c r="M45">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="N45">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="O45">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="P45">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q45">
         <v>1</v>
       </c>
       <c r="R45">
-        <v>12.438822999999999</v>
+        <v>14.225189</v>
       </c>
       <c r="S45" t="s">
         <v>28</v>
       </c>
       <c r="T45">
-        <v>2.88165E-4</v>
+        <v>2.5557200000000003E-4</v>
       </c>
       <c r="U45" t="s">
         <v>29</v>
       </c>
       <c r="V45">
-        <v>1.2415646000000001E-2</v>
+        <v>1.4184156E-2</v>
       </c>
       <c r="W45">
         <v>5</v>
       </c>
       <c r="X45">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y45">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="Z45">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>1.2160687E-2</v>
+        <v>1.4158428000000001E-2</v>
       </c>
       <c r="B46">
-        <v>2.3096446700507598</v>
+        <v>4.2182741116751199</v>
       </c>
       <c r="C46">
         <v>13.571428298950099</v>
@@ -4384,7 +4387,7 @@
         <v>25</v>
       </c>
       <c r="F46">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="G46" t="s">
         <v>26</v>
@@ -4393,66 +4396,66 @@
         <v>44</v>
       </c>
       <c r="I46">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="J46">
-        <v>52</v>
+        <v>115</v>
       </c>
       <c r="K46">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L46" t="s">
         <v>74</v>
       </c>
       <c r="M46">
-        <v>164</v>
+        <v>478</v>
       </c>
       <c r="N46">
-        <v>455</v>
+        <v>831</v>
       </c>
       <c r="O46">
-        <v>164</v>
+        <v>478</v>
       </c>
       <c r="P46">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q46">
         <v>1</v>
       </c>
       <c r="R46">
-        <v>12.729850000000001</v>
+        <v>16.768891</v>
       </c>
       <c r="S46" t="s">
         <v>28</v>
       </c>
       <c r="T46">
-        <v>5.3223799999999998E-4</v>
+        <v>2.5426049999999999E-3</v>
       </c>
       <c r="U46" t="s">
         <v>29</v>
       </c>
       <c r="V46">
-        <v>1.2692306E-2</v>
+        <v>1.6700464000000002E-2</v>
       </c>
       <c r="W46">
         <v>7</v>
       </c>
       <c r="X46">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="Y46">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="Z46">
-        <v>52</v>
+        <v>115</v>
       </c>
     </row>
     <row r="47" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>1.1914803999999999E-2</v>
+        <v>1.2838342000000001E-2</v>
       </c>
       <c r="B47">
-        <v>1.3101604278074801</v>
+        <v>1.4812834224598901</v>
       </c>
       <c r="C47">
         <v>12.857142448425201</v>
@@ -4464,7 +4467,7 @@
         <v>25</v>
       </c>
       <c r="F47">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G47" t="s">
         <v>26</v>
@@ -4473,10 +4476,10 @@
         <v>45</v>
       </c>
       <c r="I47">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="J47">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="K47">
         <v>3</v>
@@ -4485,13 +4488,13 @@
         <v>75</v>
       </c>
       <c r="M47">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="N47">
-        <v>245</v>
+        <v>277</v>
       </c>
       <c r="O47">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="P47">
         <v>5</v>
@@ -4500,39 +4503,39 @@
         <v>1</v>
       </c>
       <c r="R47">
-        <v>12.036414000000001</v>
+        <v>13.112399999999999</v>
       </c>
       <c r="S47" t="s">
         <v>28</v>
       </c>
       <c r="T47">
-        <v>1.00097E-4</v>
+        <v>1.9431400000000001E-4</v>
       </c>
       <c r="U47" t="s">
         <v>29</v>
       </c>
       <c r="V47">
-        <v>1.2014327E-2</v>
+        <v>1.3029552999999999E-2</v>
       </c>
       <c r="W47">
         <v>7</v>
       </c>
       <c r="X47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y47">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="Z47">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>1.7135258E-2</v>
+        <v>2.0992456E-2</v>
       </c>
       <c r="B48">
-        <v>2.6427672955974799</v>
+        <v>2.6641509433962201</v>
       </c>
       <c r="C48">
         <v>15.399999618530201</v>
@@ -4544,7 +4547,7 @@
         <v>25</v>
       </c>
       <c r="F48">
-        <v>395</v>
+        <v>439</v>
       </c>
       <c r="G48" t="s">
         <v>26</v>
@@ -4553,10 +4556,10 @@
         <v>46</v>
       </c>
       <c r="I48">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="J48">
-        <v>395</v>
+        <v>506</v>
       </c>
       <c r="K48">
         <v>10</v>
@@ -4565,54 +4568,54 @@
         <v>76</v>
       </c>
       <c r="M48">
-        <v>918</v>
+        <v>995</v>
       </c>
       <c r="N48">
-        <v>2101</v>
+        <v>2118</v>
       </c>
       <c r="O48">
-        <v>918</v>
+        <v>995</v>
       </c>
       <c r="P48">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="Q48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R48">
-        <v>59.057405000000003</v>
+        <v>29.021504</v>
       </c>
       <c r="S48" t="s">
         <v>28</v>
       </c>
       <c r="T48">
-        <v>4.1746469000000001E-2</v>
+        <v>7.8213529999999996E-3</v>
       </c>
       <c r="U48" t="s">
         <v>29</v>
       </c>
       <c r="V48">
-        <v>5.8881179999999998E-2</v>
+        <v>2.8813235999999999E-2</v>
       </c>
       <c r="W48">
         <v>25</v>
       </c>
       <c r="X48">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="Y48">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="Z48">
-        <v>395</v>
+        <v>506</v>
       </c>
     </row>
     <row r="49" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>1.53654449999999E-2</v>
+        <v>1.80541449999999E-2</v>
       </c>
       <c r="B49">
-        <v>2.1004273504273501</v>
+        <v>2.9871794871794801</v>
       </c>
       <c r="C49">
         <v>16.214284896850501</v>
@@ -4633,66 +4636,66 @@
         <v>47</v>
       </c>
       <c r="I49">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="J49">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="K49">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L49" t="s">
         <v>77</v>
       </c>
       <c r="M49">
-        <v>315</v>
+        <v>594</v>
       </c>
       <c r="N49">
-        <v>983</v>
+        <v>1398</v>
       </c>
       <c r="O49">
-        <v>315</v>
+        <v>594</v>
       </c>
       <c r="P49">
-        <v>97</v>
+        <v>17</v>
       </c>
       <c r="Q49">
         <v>1</v>
       </c>
       <c r="R49">
-        <v>35.180222999999998</v>
+        <v>34.741836999999997</v>
       </c>
       <c r="S49" t="s">
         <v>28</v>
       </c>
       <c r="T49">
-        <v>1.9697075000000001E-2</v>
+        <v>1.6530961E-2</v>
       </c>
       <c r="U49" t="s">
         <v>29</v>
       </c>
       <c r="V49">
-        <v>3.5061993999999999E-2</v>
+        <v>3.4584561E-2</v>
       </c>
       <c r="W49">
         <v>14</v>
       </c>
       <c r="X49">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z49">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="50" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>4.9152964999999701E-2</v>
+        <v>7.2487281999999903E-2</v>
       </c>
       <c r="B50">
-        <v>5.1568785197103697</v>
+        <v>6.9332260659694196</v>
       </c>
       <c r="C50">
         <v>20.931034088134702</v>
@@ -4704,7 +4707,7 @@
         <v>33</v>
       </c>
       <c r="F50">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="G50" t="s">
         <v>26</v>
@@ -4713,66 +4716,66 @@
         <v>48</v>
       </c>
       <c r="I50">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="J50">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="K50">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L50" t="s">
         <v>78</v>
       </c>
       <c r="M50">
-        <v>3879</v>
+        <v>5609</v>
       </c>
       <c r="N50">
-        <v>6410</v>
+        <v>8618</v>
       </c>
       <c r="O50">
-        <v>3879</v>
+        <v>5609</v>
       </c>
       <c r="P50">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="Q50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R50">
-        <v>3922.7497109999999</v>
+        <v>1070.427541</v>
       </c>
       <c r="S50" t="s">
         <v>28</v>
       </c>
       <c r="T50">
-        <v>3.8731713800000001</v>
+        <v>0.99730370000000002</v>
       </c>
       <c r="U50" t="s">
         <v>29</v>
       </c>
       <c r="V50">
-        <v>3.9223238029999998</v>
+        <v>1.0697902290000001</v>
       </c>
       <c r="W50">
         <v>29</v>
       </c>
       <c r="X50">
-        <v>88</v>
+        <v>145</v>
       </c>
       <c r="Y50">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="Z50">
-        <v>85</v>
+        <v>112</v>
       </c>
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>2.9385184000000099E-2</v>
+        <v>6.0011446999999898E-2</v>
       </c>
       <c r="B51">
-        <v>5.5046153846153798</v>
+        <v>7.3753846153846103</v>
       </c>
       <c r="C51">
         <v>19</v>
@@ -4784,7 +4787,7 @@
         <v>33</v>
       </c>
       <c r="F51">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G51" t="s">
         <v>26</v>
@@ -4793,66 +4796,66 @@
         <v>49</v>
       </c>
       <c r="I51">
-        <v>131</v>
+        <v>198</v>
       </c>
       <c r="J51">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K51">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L51" t="s">
         <v>79</v>
       </c>
       <c r="M51">
-        <v>3254</v>
+        <v>4652</v>
       </c>
       <c r="N51">
-        <v>5367</v>
+        <v>7191</v>
       </c>
       <c r="O51">
-        <v>3254</v>
+        <v>4652</v>
       </c>
       <c r="P51">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="Q51">
         <v>1</v>
       </c>
       <c r="R51">
-        <v>2155.8766799999999</v>
+        <v>996.10663099999999</v>
       </c>
       <c r="S51" t="s">
         <v>28</v>
       </c>
       <c r="T51">
-        <v>2.12610615</v>
+        <v>0.93559867600000002</v>
       </c>
       <c r="U51" t="s">
         <v>29</v>
       </c>
       <c r="V51">
-        <v>2.1554906639999998</v>
+        <v>0.99560948699999996</v>
       </c>
       <c r="W51">
         <v>25</v>
       </c>
       <c r="X51">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="Z51">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="52" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>2.0534230000000001E-2</v>
+        <v>2.6949388000000001E-2</v>
       </c>
       <c r="B52">
-        <v>3.8934426229508099</v>
+        <v>3.8579234972677501</v>
       </c>
       <c r="C52">
         <v>22.375</v>
@@ -4864,7 +4867,7 @@
         <v>33</v>
       </c>
       <c r="F52">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G52" t="s">
         <v>26</v>
@@ -4873,10 +4876,10 @@
         <v>50</v>
       </c>
       <c r="I52">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="J52">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K52">
         <v>13</v>
@@ -4885,34 +4888,34 @@
         <v>80</v>
       </c>
       <c r="M52">
-        <v>1714</v>
+        <v>1703</v>
       </c>
       <c r="N52">
-        <v>2850</v>
+        <v>2824</v>
       </c>
       <c r="O52">
-        <v>1714</v>
+        <v>1703</v>
       </c>
       <c r="P52">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="Q52">
         <v>1</v>
       </c>
       <c r="R52">
-        <v>156.93258299999999</v>
+        <v>59.066240000000001</v>
       </c>
       <c r="S52" t="s">
         <v>28</v>
       </c>
       <c r="T52">
-        <v>0.13620489199999999</v>
+        <v>3.1939243999999999E-2</v>
       </c>
       <c r="U52" t="s">
         <v>29</v>
       </c>
       <c r="V52">
-        <v>0.156738549</v>
+        <v>5.8887924000000001E-2</v>
       </c>
       <c r="W52">
         <v>16</v>
@@ -4921,18 +4924,18 @@
         <v>65</v>
       </c>
       <c r="Y52">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="Z52">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>1.5589822999999999E-2</v>
+        <v>2.0563113000000001E-2</v>
       </c>
       <c r="B53">
-        <v>2.59963768115942</v>
+        <v>3.88768115942029</v>
       </c>
       <c r="C53">
         <v>19.214284896850501</v>
@@ -4944,7 +4947,7 @@
         <v>33</v>
       </c>
       <c r="F53">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G53" t="s">
         <v>26</v>
@@ -4953,66 +4956,66 @@
         <v>51</v>
       </c>
       <c r="I53">
-        <v>79</v>
+        <v>126</v>
       </c>
       <c r="J53">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="K53">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="L53" t="s">
         <v>81</v>
       </c>
       <c r="M53">
-        <v>738</v>
+        <v>1332</v>
       </c>
       <c r="N53">
-        <v>1435</v>
+        <v>2146</v>
       </c>
       <c r="O53">
-        <v>738</v>
+        <v>1332</v>
       </c>
       <c r="P53">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="Q53">
         <v>1</v>
       </c>
       <c r="R53">
-        <v>23.240081</v>
+        <v>31.716556000000001</v>
       </c>
       <c r="S53" t="s">
         <v>28</v>
       </c>
       <c r="T53">
-        <v>7.5863279999999998E-3</v>
+        <v>1.1015394E-2</v>
       </c>
       <c r="U53" t="s">
         <v>29</v>
       </c>
       <c r="V53">
-        <v>2.3175567000000001E-2</v>
+        <v>3.1577947000000002E-2</v>
       </c>
       <c r="W53">
         <v>14</v>
       </c>
       <c r="X53">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="Y53">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="Z53">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="54" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>1.4780801999999999E-2</v>
+        <v>1.7748154999999901E-2</v>
       </c>
       <c r="B54">
-        <v>2.86075949367088</v>
+        <v>3.48101265822784</v>
       </c>
       <c r="C54">
         <v>19.25</v>
@@ -5024,7 +5027,7 @@
         <v>33</v>
       </c>
       <c r="F54">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G54" t="s">
         <v>26</v>
@@ -5033,66 +5036,66 @@
         <v>52</v>
       </c>
       <c r="I54">
-        <v>65</v>
+        <v>107</v>
       </c>
       <c r="J54">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="K54">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L54" t="s">
         <v>82</v>
       </c>
       <c r="M54">
-        <v>656</v>
+        <v>896</v>
       </c>
       <c r="N54">
-        <v>1356</v>
+        <v>1650</v>
       </c>
       <c r="O54">
-        <v>656</v>
+        <v>896</v>
       </c>
       <c r="P54">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="Q54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R54">
-        <v>20.425232000000001</v>
+        <v>23.573253999999999</v>
       </c>
       <c r="S54" t="s">
         <v>28</v>
       </c>
       <c r="T54">
-        <v>5.5881849999999999E-3</v>
+        <v>5.7085879999999997E-3</v>
       </c>
       <c r="U54" t="s">
         <v>29</v>
       </c>
       <c r="V54">
-        <v>2.0368501000000001E-2</v>
+        <v>2.3456109999999999E-2</v>
       </c>
       <c r="W54">
         <v>12</v>
       </c>
       <c r="X54">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="Y54">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="Z54">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="55" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>1.2767133E-2</v>
+        <v>1.1662713E-2</v>
       </c>
       <c r="B55">
-        <v>1.6732026143790799</v>
+        <v>1.05228758169934</v>
       </c>
       <c r="C55">
         <v>18.625</v>
@@ -5113,55 +5116,55 @@
         <v>53</v>
       </c>
       <c r="I55">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="J55">
         <v>15</v>
       </c>
       <c r="K55">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L55" t="s">
         <v>83</v>
       </c>
       <c r="M55">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="N55">
-        <v>512</v>
+        <v>322</v>
       </c>
       <c r="O55">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="P55">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Q55">
         <v>1</v>
       </c>
       <c r="R55">
-        <v>13.367184999999999</v>
+        <v>11.691694999999999</v>
       </c>
       <c r="S55" t="s">
         <v>28</v>
       </c>
-      <c r="T55">
-        <v>5.7327599999999995E-4</v>
+      <c r="T55" s="1">
+        <v>7.7389999999999999E-6</v>
       </c>
       <c r="U55" t="s">
         <v>29</v>
       </c>
       <c r="V55">
-        <v>1.33399E-2</v>
+        <v>1.1669868999999999E-2</v>
       </c>
       <c r="W55">
         <v>8</v>
       </c>
       <c r="X55">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Y55">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Z55">
         <v>15</v>
@@ -5169,10 +5172,10 @@
     </row>
     <row r="56" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>1.2972142000000001E-2</v>
+        <v>1.4390712E-2</v>
       </c>
       <c r="B56">
-        <v>2.32380952380952</v>
+        <v>2.4952380952380899</v>
       </c>
       <c r="C56">
         <v>12.625</v>
@@ -5184,7 +5187,7 @@
         <v>33</v>
       </c>
       <c r="F56">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G56" t="s">
         <v>26</v>
@@ -5193,10 +5196,10 @@
         <v>54</v>
       </c>
       <c r="I56">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="J56">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="K56">
         <v>6</v>
@@ -5205,54 +5208,54 @@
         <v>84</v>
       </c>
       <c r="M56">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="N56">
-        <v>488</v>
+        <v>524</v>
       </c>
       <c r="O56">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="P56">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Q56">
         <v>1</v>
       </c>
       <c r="R56">
-        <v>14.259895999999999</v>
+        <v>16.071831</v>
       </c>
       <c r="S56" t="s">
         <v>28</v>
       </c>
       <c r="T56">
-        <v>1.259877E-3</v>
+        <v>1.6429229999999999E-3</v>
       </c>
       <c r="U56" t="s">
         <v>29</v>
       </c>
       <c r="V56">
-        <v>1.4231436E-2</v>
+        <v>1.6032963000000001E-2</v>
       </c>
       <c r="W56">
         <v>8</v>
       </c>
       <c r="X56">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Y56">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="Z56">
-        <v>16</v>
+        <v>31</v>
       </c>
     </row>
     <row r="57" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>2.509167046</v>
+        <v>0.14652020499999999</v>
       </c>
       <c r="B57">
-        <v>46.643051771117101</v>
+        <v>20.408719346049001</v>
       </c>
       <c r="C57">
         <v>19.888889312744102</v>
@@ -5263,6 +5266,9 @@
       <c r="E57">
         <v>33</v>
       </c>
+      <c r="F57">
+        <v>233</v>
+      </c>
       <c r="G57" t="s">
         <v>26</v>
       </c>
@@ -5270,66 +5276,66 @@
         <v>55</v>
       </c>
       <c r="I57">
-        <v>4717</v>
+        <v>387</v>
       </c>
       <c r="J57">
-        <v>171</v>
+        <v>233</v>
       </c>
       <c r="K57">
-        <v>601</v>
+        <v>159</v>
       </c>
       <c r="L57" t="s">
         <v>85</v>
       </c>
       <c r="M57">
-        <v>133283</v>
+        <v>17629</v>
       </c>
       <c r="N57">
-        <v>51354</v>
+        <v>22470</v>
       </c>
       <c r="O57">
-        <v>133283</v>
+        <v>17629</v>
       </c>
       <c r="P57">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="Q57">
-        <v>841</v>
+        <v>1</v>
       </c>
       <c r="R57">
-        <v>121261.000396</v>
+        <v>1290.6494560000001</v>
       </c>
       <c r="S57" t="s">
         <v>28</v>
       </c>
       <c r="T57">
-        <v>118.751833941</v>
+        <v>1.142068337</v>
       </c>
       <c r="U57" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="V57">
-        <v>121.261000396</v>
+        <v>1.2885878989999999</v>
       </c>
       <c r="W57">
         <v>27</v>
       </c>
       <c r="X57">
-        <v>3787</v>
+        <v>337</v>
       </c>
       <c r="Y57">
         <v>0</v>
       </c>
       <c r="Z57">
-        <v>172</v>
+        <v>233</v>
       </c>
     </row>
     <row r="58" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>2.7366004999999902E-2</v>
+        <v>3.2238055999999897E-2</v>
       </c>
       <c r="B58">
-        <v>4.3454987834549801</v>
+        <v>3.6386861313868599</v>
       </c>
       <c r="C58">
         <v>20.049999237060501</v>
@@ -5341,7 +5347,7 @@
         <v>33</v>
       </c>
       <c r="F58">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G58" t="s">
         <v>26</v>
@@ -5350,66 +5356,66 @@
         <v>56</v>
       </c>
       <c r="I58">
-        <v>159</v>
+        <v>86</v>
       </c>
       <c r="J58">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="K58">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="L58" t="s">
         <v>86</v>
       </c>
       <c r="M58">
-        <v>2127</v>
+        <v>1641</v>
       </c>
       <c r="N58">
-        <v>3572</v>
+        <v>2991</v>
       </c>
       <c r="O58">
-        <v>2127</v>
+        <v>1641</v>
       </c>
       <c r="P58">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="Q58">
         <v>1</v>
       </c>
       <c r="R58">
-        <v>351.73174</v>
+        <v>42.276257999999999</v>
       </c>
       <c r="S58" t="s">
         <v>28</v>
       </c>
       <c r="T58">
-        <v>0.32412264200000002</v>
+        <v>9.8278700000000007E-3</v>
       </c>
       <c r="U58" t="s">
         <v>29</v>
       </c>
       <c r="V58">
-        <v>0.35148791600000001</v>
+        <v>4.2065377000000001E-2</v>
       </c>
       <c r="W58">
         <v>20</v>
       </c>
       <c r="X58">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="Y58">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Z58">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="59" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>1.7889067000000002E-2</v>
+        <v>1.6396574000000001E-2</v>
       </c>
       <c r="B59">
-        <v>2.83464566929133</v>
+        <v>2.54330708661417</v>
       </c>
       <c r="C59">
         <v>18.176469802856399</v>
@@ -5421,7 +5427,7 @@
         <v>33</v>
       </c>
       <c r="F59">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G59" t="s">
         <v>26</v>
@@ -5430,66 +5436,66 @@
         <v>57</v>
       </c>
       <c r="I59">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="J59">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="K59">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L59" t="s">
         <v>87</v>
       </c>
       <c r="M59">
-        <v>850</v>
+        <v>702</v>
       </c>
       <c r="N59">
-        <v>1800</v>
+        <v>1615</v>
       </c>
       <c r="O59">
-        <v>850</v>
+        <v>702</v>
       </c>
       <c r="P59">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="Q59">
         <v>1</v>
       </c>
       <c r="R59">
-        <v>35.679290999999999</v>
+        <v>18.808523999999998</v>
       </c>
       <c r="S59" t="s">
         <v>28</v>
       </c>
       <c r="T59">
-        <v>1.7669678000000001E-2</v>
+        <v>2.2943199999999999E-3</v>
       </c>
       <c r="U59" t="s">
         <v>29</v>
       </c>
       <c r="V59">
-        <v>3.5557973E-2</v>
+        <v>1.8690248999999999E-2</v>
       </c>
       <c r="W59">
         <v>17</v>
       </c>
       <c r="X59">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="Y59">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Z59">
-        <v>41</v>
+        <v>63</v>
       </c>
     </row>
     <row r="60" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>6.5473780000004894E-2</v>
+        <v>1.06998475600002</v>
       </c>
       <c r="B60">
-        <v>12.543960558750999</v>
+        <v>83.847165160230006</v>
       </c>
       <c r="C60">
         <v>20.482759475708001</v>
@@ -5507,52 +5513,52 @@
         <v>58</v>
       </c>
       <c r="I60">
-        <v>189</v>
+        <v>1512</v>
       </c>
       <c r="J60">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="K60">
-        <v>124</v>
+        <v>822</v>
       </c>
       <c r="L60" t="s">
         <v>88</v>
       </c>
       <c r="M60">
-        <v>9329</v>
+        <v>116403</v>
       </c>
       <c r="N60">
-        <v>15266</v>
+        <v>102042</v>
       </c>
       <c r="O60">
-        <v>9329</v>
+        <v>116403</v>
       </c>
       <c r="P60">
-        <v>95</v>
+        <v>15</v>
       </c>
       <c r="Q60">
         <v>1</v>
       </c>
       <c r="R60">
-        <v>120320.277829</v>
+        <v>132150.78556399999</v>
       </c>
       <c r="S60" t="s">
         <v>28</v>
       </c>
       <c r="T60">
-        <v>120.254804568</v>
+        <v>131.08080145599999</v>
       </c>
       <c r="U60" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="V60">
-        <v>120.32027782900001</v>
+        <v>132.15078556399999</v>
       </c>
       <c r="W60">
         <v>29</v>
       </c>
       <c r="X60">
-        <v>92</v>
+        <v>1495</v>
       </c>
       <c r="Y60">
         <v>0</v>
@@ -5563,10 +5569,10 @@
     </row>
     <row r="61" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>6.7418371999991594E-2</v>
+        <v>0.539101779000006</v>
       </c>
       <c r="B61">
-        <v>13.556270096463001</v>
+        <v>60.580385852089996</v>
       </c>
       <c r="C61">
         <v>21.714284896850501</v>
@@ -5577,6 +5583,9 @@
       <c r="E61">
         <v>33</v>
       </c>
+      <c r="F61">
+        <v>255</v>
+      </c>
       <c r="G61" t="s">
         <v>26</v>
       </c>
@@ -5584,66 +5593,66 @@
         <v>59</v>
       </c>
       <c r="I61">
-        <v>206</v>
+        <v>726</v>
       </c>
       <c r="J61">
-        <v>126</v>
+        <v>255</v>
       </c>
       <c r="K61">
-        <v>93</v>
+        <v>603</v>
       </c>
       <c r="L61" t="s">
         <v>89</v>
       </c>
       <c r="M61">
-        <v>9671</v>
+        <v>69567</v>
       </c>
       <c r="N61">
-        <v>16864</v>
+        <v>75362</v>
       </c>
       <c r="O61">
-        <v>9671</v>
+        <v>69567</v>
       </c>
       <c r="P61">
-        <v>120</v>
+        <v>14</v>
       </c>
       <c r="Q61">
         <v>1</v>
       </c>
       <c r="R61">
-        <v>124382.23842199999</v>
+        <v>102587.425884</v>
       </c>
       <c r="S61" t="s">
         <v>28</v>
       </c>
       <c r="T61">
-        <v>124.31482079600001</v>
+        <v>107.036942122</v>
       </c>
       <c r="U61" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="V61">
-        <v>124.382238422</v>
+        <v>107.57604295</v>
       </c>
       <c r="W61">
         <v>28</v>
       </c>
       <c r="X61">
-        <v>85</v>
+        <v>710</v>
       </c>
       <c r="Y61">
         <v>0</v>
       </c>
       <c r="Z61">
-        <v>160</v>
+        <v>255</v>
       </c>
     </row>
     <row r="62" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>2.3479213999999901E-2</v>
+        <v>2.3756948999999999E-2</v>
       </c>
       <c r="B62">
-        <v>3.48753894080996</v>
+        <v>3.5498442367601202</v>
       </c>
       <c r="C62">
         <v>17.3333339691162</v>
@@ -5655,7 +5664,7 @@
         <v>25</v>
       </c>
       <c r="F62">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G62" t="s">
         <v>26</v>
@@ -5664,66 +5673,66 @@
         <v>60</v>
       </c>
       <c r="I62">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="J62">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="K62">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L62" t="s">
         <v>90</v>
       </c>
       <c r="M62">
-        <v>1257</v>
+        <v>1293</v>
       </c>
       <c r="N62">
-        <v>2239</v>
+        <v>2279</v>
       </c>
       <c r="O62">
-        <v>1257</v>
+        <v>1293</v>
       </c>
       <c r="P62">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="Q62">
         <v>1</v>
       </c>
       <c r="R62">
-        <v>419.54026800000003</v>
+        <v>92.259135000000001</v>
       </c>
       <c r="S62" t="s">
         <v>28</v>
       </c>
       <c r="T62">
-        <v>0.39445413200000001</v>
+        <v>6.8333409999999997E-2</v>
       </c>
       <c r="U62" t="s">
         <v>29</v>
       </c>
       <c r="V62">
-        <v>0.41793261900000001</v>
+        <v>9.2089775999999998E-2</v>
       </c>
       <c r="W62">
         <v>18</v>
       </c>
       <c r="X62">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="Y62">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="Z62">
-        <v>35</v>
+        <v>47</v>
       </c>
     </row>
     <row r="63" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>1.25680409999999E-2</v>
+        <v>1.32493089999999E-2</v>
       </c>
       <c r="B63">
-        <v>1.86274509803921</v>
+        <v>2.3202614379084898</v>
       </c>
       <c r="C63">
         <v>14.800000190734799</v>
@@ -5744,66 +5753,66 @@
         <v>61</v>
       </c>
       <c r="I63">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J63">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L63" t="s">
         <v>91</v>
       </c>
       <c r="M63">
-        <v>99</v>
+        <v>153</v>
       </c>
       <c r="N63">
-        <v>285</v>
+        <v>355</v>
       </c>
       <c r="O63">
-        <v>99</v>
+        <v>153</v>
       </c>
       <c r="P63">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="Q63">
         <v>1</v>
       </c>
       <c r="R63">
-        <v>13.481420999999999</v>
+        <v>14.057373999999999</v>
       </c>
       <c r="S63" t="s">
         <v>28</v>
       </c>
       <c r="T63">
-        <v>8.7817400000000001E-4</v>
+        <v>7.4378200000000002E-4</v>
       </c>
       <c r="U63" t="s">
         <v>29</v>
       </c>
       <c r="V63">
-        <v>1.3445675000000001E-2</v>
+        <v>1.3992528000000001E-2</v>
       </c>
       <c r="W63">
         <v>5</v>
       </c>
       <c r="X63">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y63">
         <v>28</v>
       </c>
       <c r="Z63">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="64" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>1.3121729E-2</v>
+        <v>1.2757661E-2</v>
       </c>
       <c r="B64">
-        <v>3.3179190751444998</v>
+        <v>2.71676300578034</v>
       </c>
       <c r="C64">
         <v>16.799999237060501</v>
@@ -5815,7 +5824,7 @@
         <v>20</v>
       </c>
       <c r="F64">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G64" t="s">
         <v>26</v>
@@ -5824,10 +5833,10 @@
         <v>62</v>
       </c>
       <c r="I64">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="J64">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K64">
         <v>10</v>
@@ -5836,54 +5845,54 @@
         <v>92</v>
       </c>
       <c r="M64">
-        <v>333</v>
+        <v>235</v>
       </c>
       <c r="N64">
-        <v>574</v>
+        <v>470</v>
       </c>
       <c r="O64">
-        <v>333</v>
+        <v>235</v>
       </c>
       <c r="P64">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q64">
         <v>1</v>
       </c>
       <c r="R64">
-        <v>14.111488</v>
+        <v>13.204010999999999</v>
       </c>
       <c r="S64" t="s">
         <v>28</v>
       </c>
       <c r="T64">
-        <v>9.6034199999999999E-4</v>
+        <v>4.2013E-4</v>
       </c>
       <c r="U64" t="s">
         <v>29</v>
       </c>
       <c r="V64">
-        <v>1.4081563E-2</v>
+        <v>1.3177222000000001E-2</v>
       </c>
       <c r="W64">
         <v>5</v>
       </c>
       <c r="X64">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Y64">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="Z64">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>2.0175024999999999E-2</v>
+        <v>1.9304509000000001E-2</v>
       </c>
       <c r="B65">
-        <v>4</v>
+        <v>3.62917933130699</v>
       </c>
       <c r="C65">
         <v>15.949999809265099</v>
@@ -5895,7 +5904,7 @@
         <v>25</v>
       </c>
       <c r="F65">
-        <v>356</v>
+        <v>389</v>
       </c>
       <c r="G65" t="s">
         <v>26</v>
@@ -5904,10 +5913,10 @@
         <v>63</v>
       </c>
       <c r="I65">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="J65">
-        <v>356</v>
+        <v>509</v>
       </c>
       <c r="K65">
         <v>17</v>
@@ -5916,54 +5925,54 @@
         <v>93</v>
       </c>
       <c r="M65">
-        <v>1451</v>
+        <v>1275</v>
       </c>
       <c r="N65">
-        <v>2632</v>
+        <v>2388</v>
       </c>
       <c r="O65">
-        <v>1451</v>
+        <v>1275</v>
       </c>
       <c r="P65">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="Q65">
         <v>1</v>
       </c>
       <c r="R65">
-        <v>638.89123900000004</v>
+        <v>26.122789000000001</v>
       </c>
       <c r="S65" t="s">
         <v>28</v>
       </c>
       <c r="T65">
-        <v>0.618495876</v>
+        <v>6.6236849999999998E-3</v>
       </c>
       <c r="U65" t="s">
         <v>29</v>
       </c>
       <c r="V65">
-        <v>0.638670179</v>
+        <v>2.5927427999999999E-2</v>
       </c>
       <c r="W65">
         <v>20</v>
       </c>
       <c r="X65">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Y65">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z65">
-        <v>356</v>
+        <v>509</v>
       </c>
     </row>
     <row r="66" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>1.37441589999999E-2</v>
+        <v>1.5095848E-2</v>
       </c>
       <c r="B66">
-        <v>4.1803278688524497</v>
+        <v>4.9016393442622901</v>
       </c>
       <c r="C66">
         <v>17.799999237060501</v>
@@ -5975,7 +5984,7 @@
         <v>25</v>
       </c>
       <c r="F66">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G66" t="s">
         <v>26</v>
@@ -5984,66 +5993,66 @@
         <v>64</v>
       </c>
       <c r="I66">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="J66">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K66">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="L66" t="s">
         <v>94</v>
       </c>
       <c r="M66">
-        <v>419</v>
+        <v>517</v>
       </c>
       <c r="N66">
-        <v>765</v>
+        <v>897</v>
       </c>
       <c r="O66">
-        <v>419</v>
+        <v>517</v>
       </c>
       <c r="P66">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q66">
         <v>1</v>
       </c>
       <c r="R66">
-        <v>16.161183000000001</v>
+        <v>18.855817999999999</v>
       </c>
       <c r="S66" t="s">
         <v>28</v>
       </c>
       <c r="T66">
-        <v>2.3856760000000002E-3</v>
+        <v>3.667614E-3</v>
       </c>
       <c r="U66" t="s">
         <v>29</v>
       </c>
       <c r="V66">
-        <v>1.6129243000000001E-2</v>
+        <v>1.8762754999999999E-2</v>
       </c>
       <c r="W66">
         <v>5</v>
       </c>
       <c r="X66">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Y66">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="Z66">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>1.2334893E-2</v>
+        <v>1.2752295E-2</v>
       </c>
       <c r="B67">
-        <v>1.8535031847133701</v>
+        <v>1.95541401273885</v>
       </c>
       <c r="C67">
         <v>15.199999809265099</v>
@@ -6064,66 +6073,66 @@
         <v>65</v>
       </c>
       <c r="I67">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="J67">
+        <v>7</v>
+      </c>
+      <c r="K67">
         <v>5</v>
-      </c>
-      <c r="K67">
-        <v>4</v>
       </c>
       <c r="L67" t="s">
         <v>95</v>
       </c>
       <c r="M67">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="N67">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="O67">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="P67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q67">
         <v>1</v>
       </c>
       <c r="R67">
-        <v>12.646811</v>
+        <v>12.954561999999999</v>
       </c>
       <c r="S67" t="s">
         <v>28</v>
       </c>
       <c r="T67">
-        <v>2.8882300000000001E-4</v>
+        <v>1.78736E-4</v>
       </c>
       <c r="U67" t="s">
         <v>29</v>
       </c>
       <c r="V67">
-        <v>1.2623057E-2</v>
+        <v>1.2930418000000001E-2</v>
       </c>
       <c r="W67">
         <v>5</v>
       </c>
       <c r="X67">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y67">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="Z67">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>2.4115973999999998E-2</v>
+        <v>2.3978670000000001E-2</v>
       </c>
       <c r="B68">
-        <v>4.7685185185185102</v>
+        <v>3.5423280423280401</v>
       </c>
       <c r="C68">
         <v>15.25</v>
@@ -6135,7 +6144,7 @@
         <v>25</v>
       </c>
       <c r="F68">
-        <v>340</v>
+        <v>399</v>
       </c>
       <c r="G68" t="s">
         <v>26</v>
@@ -6144,66 +6153,66 @@
         <v>66</v>
       </c>
       <c r="I68">
-        <v>135</v>
+        <v>76</v>
       </c>
       <c r="J68">
-        <v>340</v>
+        <v>475</v>
       </c>
       <c r="K68">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="L68" t="s">
         <v>96</v>
       </c>
       <c r="M68">
-        <v>2123</v>
+        <v>1422</v>
       </c>
       <c r="N68">
-        <v>3605</v>
+        <v>2678</v>
       </c>
       <c r="O68">
-        <v>2123</v>
+        <v>1422</v>
       </c>
       <c r="P68">
-        <v>79</v>
+        <v>9</v>
       </c>
       <c r="Q68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R68">
-        <v>1648.8264819999999</v>
+        <v>36.393704999999997</v>
       </c>
       <c r="S68" t="s">
         <v>28</v>
       </c>
       <c r="T68">
-        <v>1.6244254599999901</v>
+        <v>1.2100557E-2</v>
       </c>
       <c r="U68" t="s">
         <v>29</v>
       </c>
       <c r="V68">
-        <v>1.648540841</v>
+        <v>3.6078489999999998E-2</v>
       </c>
       <c r="W68">
         <v>24</v>
       </c>
       <c r="X68">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z68">
-        <v>340</v>
+        <v>475</v>
       </c>
     </row>
     <row r="69" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>1.24958439999999E-2</v>
+        <v>1.37821259999999E-2</v>
       </c>
       <c r="B69">
-        <v>1.86330935251798</v>
+        <v>2.4388489208633</v>
       </c>
       <c r="C69">
         <v>13.399999618530201</v>
@@ -6215,7 +6224,7 @@
         <v>25</v>
       </c>
       <c r="F69">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G69" t="s">
         <v>26</v>
@@ -6224,66 +6233,66 @@
         <v>67</v>
       </c>
       <c r="I69">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="J69">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="K69">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L69" t="s">
         <v>97</v>
       </c>
       <c r="M69">
-        <v>98</v>
+        <v>160</v>
       </c>
       <c r="N69">
-        <v>259</v>
+        <v>339</v>
       </c>
       <c r="O69">
-        <v>98</v>
+        <v>160</v>
       </c>
       <c r="P69">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Q69">
         <v>1</v>
       </c>
       <c r="R69">
-        <v>13.080565999999999</v>
+        <v>14.416252999999999</v>
       </c>
       <c r="S69" t="s">
         <v>28</v>
       </c>
       <c r="T69">
-        <v>5.2652000000000005E-4</v>
+        <v>6.0550899999999995E-4</v>
       </c>
       <c r="U69" t="s">
         <v>29</v>
       </c>
       <c r="V69">
-        <v>1.3021626E-2</v>
+        <v>1.4386957000000001E-2</v>
       </c>
       <c r="W69">
         <v>5</v>
       </c>
       <c r="X69">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Y69">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="Z69">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="70" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>1.3593322E-2</v>
+        <v>1.3921427E-2</v>
       </c>
       <c r="B70">
-        <v>3.0862944162436499</v>
+        <v>3.1370558375634499</v>
       </c>
       <c r="C70">
         <v>13.571428298950099</v>
@@ -6295,7 +6304,7 @@
         <v>25</v>
       </c>
       <c r="F70">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="G70" t="s">
         <v>26</v>
@@ -6304,66 +6313,66 @@
         <v>68</v>
       </c>
       <c r="I70">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="J70">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="K70">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L70" t="s">
         <v>98</v>
       </c>
       <c r="M70">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="N70">
-        <v>608</v>
+        <v>618</v>
       </c>
       <c r="O70">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="P70">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q70">
         <v>1</v>
       </c>
       <c r="R70">
-        <v>16.498833999999999</v>
+        <v>14.856615</v>
       </c>
       <c r="S70" t="s">
         <v>28</v>
       </c>
       <c r="T70">
-        <v>2.8723260000000001E-3</v>
+        <v>8.8754800000000005E-4</v>
       </c>
       <c r="U70" t="s">
         <v>29</v>
       </c>
       <c r="V70">
-        <v>1.6465115999999998E-2</v>
+        <v>1.4808412E-2</v>
       </c>
       <c r="W70">
         <v>7</v>
       </c>
       <c r="X70">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Y70">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="Z70">
-        <v>70</v>
+        <v>123</v>
       </c>
     </row>
     <row r="71" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>1.210462E-2</v>
+        <v>1.2160298999999999E-2</v>
       </c>
       <c r="B71">
-        <v>1.50802139037433</v>
+        <v>1.3529411764705801</v>
       </c>
       <c r="C71">
         <v>12.857142448425201</v>
@@ -6375,7 +6384,7 @@
         <v>25</v>
       </c>
       <c r="F71">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G71" t="s">
         <v>26</v>
@@ -6384,66 +6393,66 @@
         <v>69</v>
       </c>
       <c r="I71">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="J71">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L71" t="s">
         <v>99</v>
       </c>
       <c r="M71">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="N71">
-        <v>282</v>
+        <v>253</v>
       </c>
       <c r="O71">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="P71">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q71">
         <v>1</v>
       </c>
       <c r="R71">
-        <v>12.504348</v>
+        <v>12.294297</v>
       </c>
       <c r="S71" t="s">
         <v>28</v>
       </c>
       <c r="T71">
-        <v>3.7884000000000003E-4</v>
+        <v>1.0185E-4</v>
       </c>
       <c r="U71" t="s">
         <v>29</v>
       </c>
       <c r="V71">
-        <v>1.2482942E-2</v>
+        <v>1.2261586999999999E-2</v>
       </c>
       <c r="W71">
         <v>7</v>
       </c>
       <c r="X71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y71">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="Z71">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="72" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>3.74645459999998E-2</v>
+        <v>2.8637152999999999E-2</v>
       </c>
       <c r="B72">
-        <v>5.1522012578616296</v>
+        <v>4.4654088050314398</v>
       </c>
       <c r="C72">
         <v>15.399999618530201</v>
@@ -6455,7 +6464,7 @@
         <v>25</v>
       </c>
       <c r="F72">
-        <v>418</v>
+        <v>469</v>
       </c>
       <c r="G72" t="s">
         <v>26</v>
@@ -6464,66 +6473,66 @@
         <v>70</v>
       </c>
       <c r="I72">
-        <v>190</v>
+        <v>109</v>
       </c>
       <c r="J72">
-        <v>418</v>
+        <v>507</v>
       </c>
       <c r="K72">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L72" t="s">
         <v>100</v>
       </c>
       <c r="M72">
-        <v>2436</v>
+        <v>2099</v>
       </c>
       <c r="N72">
-        <v>4096</v>
+        <v>3550</v>
       </c>
       <c r="O72">
-        <v>2436</v>
+        <v>2099</v>
       </c>
       <c r="P72">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="Q72">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="R72">
-        <v>5688.3979069999996</v>
+        <v>59.514242000000003</v>
       </c>
       <c r="S72" t="s">
         <v>28</v>
       </c>
       <c r="T72">
-        <v>5.6506164700000001</v>
+        <v>3.0552622000000002E-2</v>
       </c>
       <c r="U72" t="s">
         <v>29</v>
       </c>
       <c r="V72">
-        <v>5.6880803550000003</v>
+        <v>5.9189022000000001E-2</v>
       </c>
       <c r="W72">
         <v>25</v>
       </c>
       <c r="X72">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="Y72">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="Z72">
-        <v>418</v>
+        <v>507</v>
       </c>
     </row>
     <row r="73" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>2.1624462000000001E-2</v>
+        <v>0.10440878300000001</v>
       </c>
       <c r="B73">
-        <v>4.11752136752136</v>
+        <v>6.66239316239316</v>
       </c>
       <c r="C73">
         <v>16.214284896850501</v>
@@ -6535,7 +6544,7 @@
         <v>25</v>
       </c>
       <c r="F73">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="G73" t="s">
         <v>26</v>
@@ -6544,58 +6553,58 @@
         <v>71</v>
       </c>
       <c r="I73">
-        <v>167</v>
+        <v>498</v>
       </c>
       <c r="J73">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="K73">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="L73" t="s">
         <v>101</v>
       </c>
       <c r="M73">
-        <v>926</v>
+        <v>1592</v>
       </c>
       <c r="N73">
-        <v>1927</v>
+        <v>3118</v>
       </c>
       <c r="O73">
-        <v>926</v>
+        <v>1592</v>
       </c>
       <c r="P73">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="Q73">
-        <v>1</v>
+        <v>349</v>
       </c>
       <c r="R73">
-        <v>327.07881600000002</v>
+        <v>687.90124700000001</v>
       </c>
       <c r="S73" t="s">
         <v>28</v>
       </c>
       <c r="T73">
-        <v>0.30521011199999998</v>
+        <v>0.58315450800000002</v>
       </c>
       <c r="U73" t="s">
         <v>29</v>
       </c>
       <c r="V73">
-        <v>0.32683411299999998</v>
+        <v>0.68756267599999998</v>
       </c>
       <c r="W73">
         <v>14</v>
       </c>
       <c r="X73">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="Y73">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="Z73">
-        <v>105</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
